--- a/Results/Phase 2/Carbon dioxide/carbon dioxide ionising radiation results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide ionising radiation results.xlsx
@@ -2383,7 +2383,7 @@
         <v>0.02922885067998044</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02914679180067748</v>
+        <v>0.02914679180067747</v>
       </c>
       <c r="V5" t="n">
         <v>0.04953941914469908</v>
@@ -2951,7 +2951,7 @@
         <v>0.02781750198343364</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03781424582650262</v>
+        <v>0.03781424582650263</v>
       </c>
       <c r="F12" t="n">
         <v>0.09482904906045223</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004946505594303773</v>
+        <v>0.004946505594303804</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009961143896426768</v>
+        <v>0.009961143896426767</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005827916861914098</v>
+        <v>0.00582791686191398</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06294268921733007</v>
+        <v>0.06294268921733014</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07319715106836079</v>
+        <v>0.07319715106836069</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0140112885807183</v>
+        <v>0.01401128858071827</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04341386845059308</v>
+        <v>0.04341386845059315</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01354046155811509</v>
+        <v>0.01354046155811503</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03403557992406919</v>
+        <v>0.03403557992406907</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005333951870116476</v>
+        <v>0.005333951870116394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002449993565282863</v>
+        <v>0.002449993565282861</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0218444657956714</v>
+        <v>0.02184446579567138</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01736409690763146</v>
+        <v>0.01736409690763158</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1640575619134156</v>
+        <v>0.1640575619134158</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07763168779780993</v>
+        <v>0.07763168779781007</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08680025714224543</v>
+        <v>0.08680025714224532</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03263918456568232</v>
+        <v>0.03263918456568222</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003273888527688327</v>
+        <v>0.003273888527688482</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07591602277890264</v>
+        <v>0.07591602277890246</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04112197083261322</v>
+        <v>0.04112197083261311</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06201274897218412</v>
+        <v>0.0620127489721841</v>
       </c>
       <c r="W2" t="n">
         <v>0.1020927914140176</v>
       </c>
       <c r="X2" t="n">
-        <v>0.006455669961181515</v>
+        <v>0.006455669961181466</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09233777158602327</v>
+        <v>0.09233777158602323</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04829354605410863</v>
+        <v>0.04829354605410854</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01719768232334648</v>
+        <v>0.01719768232334638</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00894003295328981</v>
+        <v>0.008940032953289809</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001633705217703577</v>
+        <v>0.001633705217703492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001899440661221613</v>
+        <v>0.001899440661221614</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001743411502596112</v>
+        <v>0.001743411502596114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001765657323874907</v>
+        <v>0.001765657323874908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002105113494428471</v>
+        <v>0.002105113494428578</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001983104641478271</v>
+        <v>0.001983104641478224</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001905882793438799</v>
+        <v>0.001905882793438802</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001721490387969485</v>
+        <v>0.0017214903879695</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00180466438349354</v>
+        <v>0.001804664383493584</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001784276427459231</v>
+        <v>0.001784276427459371</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001556973544462672</v>
+        <v>0.001556973544462574</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001833823744020958</v>
+        <v>0.001833823744020908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001832795875332897</v>
+        <v>0.001832795875332877</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002024228576475347</v>
+        <v>0.002024228576475271</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001592758753122709</v>
+        <v>0.00159275875312266</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00241278091463308</v>
+        <v>0.002412780914633095</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001626452471234726</v>
+        <v>0.001626452471234703</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002024151843165202</v>
+        <v>0.002024151843165269</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002284422722242129</v>
+        <v>0.002284422722242131</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02857948269436167</v>
+        <v>0.02857948269436156</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03032800405007178</v>
+        <v>0.03032800405007172</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02890074675135201</v>
+        <v>0.02890074675135183</v>
       </c>
       <c r="E4" t="n">
         <v>0.04967212054043899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05350124235697961</v>
+        <v>0.0535012423569795</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03188348964885383</v>
+        <v>0.03188348964885369</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04260038474889876</v>
+        <v>0.04260038474889865</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03171187872784497</v>
+        <v>0.03171187872784481</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0429091036132172</v>
+        <v>0.04290910361321702</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02872070231227151</v>
+        <v>0.02872070231227137</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02766953337530791</v>
+        <v>0.02766953337530774</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03466342939200658</v>
+        <v>0.03466342939200642</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0331055489133505</v>
+        <v>0.03310554891335042</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08657359434632431</v>
+        <v>0.08657359434632428</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0550723780950382</v>
+        <v>0.05507237809503795</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05841421395830806</v>
+        <v>0.05841421395830789</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0386731389955748</v>
+        <v>0.03867313899557465</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02796983341444155</v>
+        <v>0.0279698334144414</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0544470383420023</v>
+        <v>0.05444703834200208</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04176501497996583</v>
+        <v>0.04176501497996561</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0743651091541888</v>
+        <v>0.07436510915418881</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06398816312636527</v>
+        <v>0.06398816312636509</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02912955538458587</v>
+        <v>0.02912955538458585</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06043257294828747</v>
+        <v>0.06043257294828739</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04437896993531282</v>
+        <v>0.04437896993531264</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03304489275151737</v>
+        <v>0.03304489275151722</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02994128562173445</v>
+        <v>0.02994128562173425</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02737200585795689</v>
+        <v>0.02737200585795677</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02738960788613837</v>
+        <v>0.02738960788613828</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02736570245161988</v>
+        <v>0.02736570245161984</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02746530167806295</v>
+        <v>0.02746530167806273</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0275438286392677</v>
+        <v>0.02754382863926763</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03122635275187996</v>
+        <v>0.03122635275187997</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02739605001835516</v>
+        <v>0.02739605001835502</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02740400252169347</v>
+        <v>0.02740400252169322</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02743431846638358</v>
+        <v>0.02743431846638342</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02742688729581658</v>
+        <v>0.02742688729581639</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02734403806408931</v>
+        <v>0.02734403806408924</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02744494671088917</v>
+        <v>0.02744494671088921</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05243022291907402</v>
+        <v>0.05243022291907417</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02751434703647247</v>
+        <v>0.02751434703647227</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02735708135243495</v>
+        <v>0.02735708135243476</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02765596980111897</v>
+        <v>0.02765596980111889</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02736936231703519</v>
+        <v>0.02736936231703496</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02751431906808195</v>
+        <v>0.02751431906808188</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02751539384663862</v>
+        <v>0.0275153938466386</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002485374013739956</v>
+        <v>0.002485374013739935</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004233895369450026</v>
+        <v>0.00423389536945003</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002806638070730271</v>
+        <v>0.002806638070730213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02357801185981728</v>
+        <v>0.02357801185981732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02740713367635787</v>
+        <v>0.02740713367635785</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005754666610874242</v>
+        <v>0.005754666610874141</v>
       </c>
       <c r="H6" t="n">
         <v>0.01650627606827703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005617770047223265</v>
+        <v>0.005617770047223206</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01302869595425414</v>
+        <v>0.01302869595425409</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002626593631649813</v>
+        <v>0.002626593631649764</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00157542469468616</v>
+        <v>0.001575424694686087</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0085693207113848</v>
+        <v>0.008569320711384798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007011440232728814</v>
+        <v>0.007011440232728807</v>
       </c>
       <c r="O6" t="n">
         <v>0.06044477130834468</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0289435550570586</v>
+        <v>0.0289435550570585</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03232010527768631</v>
+        <v>0.03232010527768623</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01257903031495311</v>
+        <v>0.01257903031495308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001875724733819854</v>
+        <v>0.001875724733819796</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02835292966138057</v>
+        <v>0.02835292966138054</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01563619194198608</v>
+        <v>0.01563619194198607</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02319908201954196</v>
+        <v>0.023199082019542</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03785934008838567</v>
+        <v>0.03785934008838561</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003000732346606264</v>
+        <v>0.003000732346606166</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03433846426766581</v>
+        <v>0.03433846426766576</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01828486125469109</v>
+        <v>0.01828486125469102</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006950784070895655</v>
+        <v>0.006950784070895606</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00384717694111262</v>
+        <v>0.003847176941112622</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001277897177335224</v>
+        <v>0.001277897177335174</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001295499205516579</v>
+        <v>0.001295499205516582</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001271593770998198</v>
+        <v>0.001271593770998197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00137119299744108</v>
+        <v>0.001371192997441081</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001415005601288006</v>
+        <v>0.001415005601288103</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460228</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460228</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001345945092917145</v>
+        <v>0.001345945092917053</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460229</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460228</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001301941337733384</v>
+        <v>0.001301941337733383</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001309893841071673</v>
+        <v>0.001309893841071602</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001305495428403924</v>
+        <v>0.001305495428403868</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001298064257836928</v>
+        <v>0.001298064257836868</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001249929383467612</v>
+        <v>0.001249929383467665</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460228</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460229</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001316123672909547</v>
+        <v>0.001316123672909587</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001264195784427143</v>
+        <v>0.001264195784427163</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001385523998492777</v>
+        <v>0.001385523998492778</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001228258314455305</v>
+        <v>0.001228258314455214</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001561861120497209</v>
+        <v>0.001561861120497298</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001275253636413395</v>
+        <v>0.001275253636413335</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001420210387460177</v>
+        <v>0.001420210387460228</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001421285166016907</v>
+        <v>0.00142128516601691</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001739247176338166</v>
+        <v>0.001739247176338167</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003781536461109732</v>
+        <v>0.003781536461109739</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005315033201274065</v>
+        <v>0.00531503320127407</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01083830745766549</v>
+        <v>0.01083830745766548</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006262288525859072</v>
+        <v>0.006262288525859108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06772198546403399</v>
+        <v>0.06772198546403413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07858776760941509</v>
+        <v>0.07858776760941498</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01505698257908142</v>
+        <v>0.01505698257908147</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04665602307442976</v>
+        <v>0.04665602307442979</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01455098337018931</v>
+        <v>0.01455098337018933</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0366212619057113</v>
+        <v>0.03662126190571133</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005731422872294783</v>
+        <v>0.005731422872294791</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00263202425949811</v>
+        <v>0.002632024259498122</v>
       </c>
       <c r="M9" t="n">
         <v>0.02360242565333525</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01866025571239653</v>
+        <v>0.01866025571239659</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1763121611450225</v>
+        <v>0.1763121611450227</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08343001583290334</v>
+        <v>0.08343001583290315</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09328350471998091</v>
+        <v>0.0932835047199809</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03507643808866765</v>
+        <v>0.03507643808866764</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003517466638914543</v>
+        <v>0.003517466638914581</v>
       </c>
       <c r="T9" t="n">
-        <v>0.081586185507509</v>
+        <v>0.08158618550750893</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0441929138519652</v>
+        <v>0.04419291385196535</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06673554839267126</v>
+        <v>0.06673554839267139</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1097184370241813</v>
+        <v>0.1097184370241811</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00693693665852703</v>
+        <v>0.006936936658526898</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09923468804902602</v>
+        <v>0.09923468804902605</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05190022718441379</v>
+        <v>0.0519002271844138</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01848140946111137</v>
+        <v>0.01848140946111135</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009765497174712189</v>
+        <v>0.009765497174712187</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001754756731777971</v>
+        <v>0.001754756731777975</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001950938727576994</v>
+        <v>0.001950938727576996</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001820127713030728</v>
+        <v>0.001820127713030734</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002261380616212695</v>
+        <v>0.002261380616212697</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002174370887537763</v>
+        <v>0.002174370887537766</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001849099716727013</v>
+        <v>0.001849099716727019</v>
       </c>
       <c r="O10" t="n">
         <v>0.001938487058394206</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001916576061087376</v>
+        <v>0.001916576061087381</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001672292973130052</v>
+        <v>0.001672292973130053</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="S10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="T10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001969824710334922</v>
+        <v>0.001969824710334927</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002059972870676711</v>
+        <v>0.002059972870676714</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002174453353054806</v>
+        <v>0.002174453353054809</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001710751443869307</v>
+        <v>0.00171075144386931</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002592031712584765</v>
+        <v>0.002592031712584768</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001746962183463362</v>
+        <v>0.001746962183463364</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.002174370887537113</v>
+        <v>0.002174370887537116</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.002612692960153794</v>
+        <v>0.002612692960153796</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02810980085221265</v>
+        <v>0.02810980085221246</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02387879282627551</v>
+        <v>0.02387879282627539</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04641350619815176</v>
+        <v>0.04641350619815162</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02488262995263218</v>
+        <v>0.02488262995263196</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02563638260285773</v>
+        <v>0.0256363826028577</v>
       </c>
       <c r="C12" t="n">
-        <v>0.028351212376954</v>
+        <v>0.02835121237695389</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02610198268706117</v>
+        <v>0.02610198268706108</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05631098687721391</v>
+        <v>0.0563109868772138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06165179515827815</v>
+        <v>0.06165179515827809</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03042479849547892</v>
+        <v>0.03042479849547883</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04595653057819705</v>
+        <v>0.04595653057819692</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03017608701489657</v>
+        <v>0.03017608701489647</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04425136114264788</v>
+        <v>0.04425136114264781</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02584104871647776</v>
+        <v>0.02584104871647766</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02431761546923741</v>
+        <v>0.02431761546923736</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03462510110836895</v>
+        <v>0.03462510110836875</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03219589888492732</v>
+        <v>0.03219589888492714</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1096858200700347</v>
+        <v>0.1096858200700348</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06403188331621798</v>
+        <v>0.06403188331621787</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.06887512371450343</v>
+        <v>0.06887512371450336</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04026487004646669</v>
+        <v>0.04026487004646656</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02475283291876115</v>
+        <v>0.02475283291876111</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06312559381593293</v>
+        <v>0.06312559381593272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04474584974947303</v>
+        <v>0.04474584974947309</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0773570042134536</v>
+        <v>0.07735700421345375</v>
       </c>
       <c r="W12" t="n">
-        <v>0.07695331094249935</v>
+        <v>0.07695331094249917</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02643358940303876</v>
+        <v>0.02643358940303861</v>
       </c>
       <c r="Y12" t="n">
         <v>0.07180028168110285</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.04853419027755884</v>
+        <v>0.04853419027755877</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03210799140370588</v>
+        <v>0.03210799140370577</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0278238988373904</v>
+        <v>0.02782389883739031</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02388641616723892</v>
+        <v>0.02388641616723877</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02398284460780036</v>
+        <v>0.02398284460780024</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02391854766714795</v>
+        <v>0.02391854766714792</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02413543469173825</v>
+        <v>0.02413543469173812</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0273198380966988</v>
+        <v>0.02731983809669874</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02409266719711868</v>
+        <v>0.0240926671971185</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02393278814382875</v>
+        <v>0.02393278814382867</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02397672429570549</v>
+        <v>0.02397672429570537</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02396595448325231</v>
+        <v>0.02396595448325217</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02384588313250822</v>
+        <v>0.02384588313250819</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02399212754866547</v>
+        <v>0.02399212754866549</v>
       </c>
       <c r="V13" t="n">
-        <v>0.04556731390779076</v>
+        <v>0.04556731390779069</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0240927077310177</v>
+        <v>0.02409270773101755</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02386478644901634</v>
+        <v>0.0238647864490162</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02429795811527266</v>
+        <v>0.02429795811527263</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02388258494849835</v>
+        <v>0.02388258494849827</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02409266719711836</v>
+        <v>0.02409266719711818</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02430811364394401</v>
+        <v>0.024308113643944</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002415171006283678</v>
+        <v>0.002415171006283681</v>
       </c>
       <c r="H14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="J14" t="n">
-        <v>0.002416457603123845</v>
+        <v>0.002416457603123849</v>
       </c>
       <c r="K14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="N14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="O14" t="n">
-        <v>0.002415171006283678</v>
+        <v>0.002415171006283681</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002415171006283678</v>
+        <v>0.002415171006283681</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="R14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00144118380457361</v>
+        <v>0.001441183804573615</v>
       </c>
       <c r="T14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="U14" t="n">
-        <v>0.002415171006283678</v>
+        <v>0.002415171006283681</v>
       </c>
       <c r="V14" t="n">
-        <v>0.002417241520471004</v>
+        <v>0.002417241520471006</v>
       </c>
       <c r="W14" t="n">
-        <v>0.002415171006283678</v>
+        <v>0.002415171006283681</v>
       </c>
       <c r="X14" t="n">
-        <v>0.002415171006283678</v>
+        <v>0.002415171006283681</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.002445020930930264</v>
+        <v>0.002445020930930267</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.003198773581155838</v>
+        <v>0.003198773581155821</v>
       </c>
       <c r="C15" t="n">
-        <v>0.005913603355252107</v>
+        <v>0.005913603355252117</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003664373665359299</v>
+        <v>0.00366437366535931</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03387337785551207</v>
+        <v>0.0338733778555121</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03921418613657628</v>
+        <v>0.03921418613657624</v>
       </c>
       <c r="G15" t="n">
-        <v>0.007957339549130461</v>
+        <v>0.007957339549130448</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02351892155649511</v>
+        <v>0.02351892155649518</v>
       </c>
       <c r="I15" t="n">
         <v>0.007738477993194671</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01855801789355921</v>
+        <v>0.01855801789355919</v>
       </c>
       <c r="K15" t="n">
         <v>0.003403439694775869</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001880006447535571</v>
+        <v>0.001880006447535586</v>
       </c>
       <c r="M15" t="n">
         <v>0.01218749208666705</v>
       </c>
       <c r="N15" t="n">
-        <v>0.009758289863225413</v>
+        <v>0.009758289863225416</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08721836112368619</v>
+        <v>0.08721836112368633</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04156442436986948</v>
+        <v>0.04156442436986955</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.04643751469280155</v>
+        <v>0.04643751469280154</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01782726102476482</v>
+        <v>0.01782726102476478</v>
       </c>
       <c r="S15" t="n">
-        <v>0.002315223897059237</v>
+        <v>0.002315223897059236</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04068798479423105</v>
+        <v>0.040687984794231</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02227839080312454</v>
+        <v>0.02227839080312456</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03336073953577288</v>
+        <v>0.0333607395357729</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05448585199615081</v>
+        <v>0.05448585199615086</v>
       </c>
       <c r="X15" t="n">
-        <v>0.00396613045669028</v>
+        <v>0.003966130456690294</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.049362672659401</v>
+        <v>0.04936267265940104</v>
       </c>
       <c r="Z15" t="n">
         <v>0.02609658125585694</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.009670382382003996</v>
+        <v>0.009670382382003994</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.005386289815688517</v>
+        <v>0.005386289815688523</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001448807145537036</v>
+        <v>0.001448807145537039</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001545235586098448</v>
+        <v>0.001545235586098451</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001480938645446082</v>
+        <v>0.001480938645446084</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001667975745389775</v>
+        <v>0.001667975745389776</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001626494847610031</v>
+        <v>0.001626494847610033</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001655058175416771</v>
+        <v>0.001655058175416773</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001495179122126899</v>
+        <v>0.001495179122126902</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001509265349356999</v>
+        <v>0.001509265349357001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.001498495536903836</v>
+        <v>0.001498495536903838</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.001408274110806377</v>
+        <v>0.00140827411080638</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="T16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="U16" t="n">
-        <v>0.001524668602317048</v>
+        <v>0.001524668602317051</v>
       </c>
       <c r="V16" t="n">
-        <v>0.001571049230110029</v>
+        <v>0.001571049230110031</v>
       </c>
       <c r="W16" t="n">
-        <v>0.00162524878466921</v>
+        <v>0.001625248784669213</v>
       </c>
       <c r="X16" t="n">
-        <v>0.001397327502667806</v>
+        <v>0.001397327502667808</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.00186034909357082</v>
+        <v>0.001860349093570824</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001444975926796513</v>
+        <v>0.001444975926796515</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.001655058175416451</v>
+        <v>0.001655058175416454</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001870504622242144</v>
+        <v>0.001870504622242147</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006836386566817869</v>
+        <v>0.006836386566817811</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007331190709214731</v>
+        <v>0.007331190709214733</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01808861791171807</v>
+        <v>0.01808861791171793</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02075330402640497</v>
+        <v>0.020753304026405</v>
       </c>
       <c r="F2" t="n">
         <v>0.105313664932287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01558065647748856</v>
+        <v>0.01558065647748843</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04187499208290335</v>
+        <v>0.04187499208290346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05412458335326303</v>
+        <v>0.05412458335326305</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03255732637029933</v>
+        <v>0.03255732637029927</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04254122616736903</v>
+        <v>0.04254122616736904</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03761848344264426</v>
+        <v>0.03761848344264395</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04702605625434908</v>
+        <v>0.047026056254349</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01387067931008678</v>
+        <v>0.01387067931008668</v>
       </c>
       <c r="O2" t="n">
         <v>0.1185507360201302</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05816170088682011</v>
+        <v>0.05816170088681998</v>
       </c>
       <c r="Q2" t="n">
         <v>0.1032352469333979</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04447315477027913</v>
+        <v>0.04447315477027911</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03547056747259118</v>
+        <v>0.03547056747259108</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0847066356876533</v>
+        <v>0.08470663568765331</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02030700751107865</v>
+        <v>0.0203070075110785</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01922386513776723</v>
+        <v>0.01922386513776722</v>
       </c>
       <c r="W2" t="n">
-        <v>0.07694935175343073</v>
+        <v>0.07694935175343062</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0164263645902531</v>
+        <v>0.01642636459025301</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02441707055723702</v>
+        <v>0.02441707055723691</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01546664075825937</v>
+        <v>0.01546664075825935</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01842157545645709</v>
+        <v>0.01842157545645711</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007371619550311029</v>
+        <v>0.007371619550311041</v>
       </c>
     </row>
     <row r="3">
@@ -6578,82 +6578,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001280665717425803</v>
+        <v>0.001280665717425734</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001539073537555746</v>
+        <v>0.001539073537555747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001347365789062439</v>
+        <v>0.001347365789062437</v>
       </c>
       <c r="F3" t="n">
         <v>0.0015775886340017</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001679651893527363</v>
+        <v>0.001679651893527413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001573112221629641</v>
+        <v>0.001573112221629655</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001625469030649985</v>
+        <v>0.001625469030649984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001354964517703652</v>
+        <v>0.001354964517703595</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001425360554560593</v>
+        <v>0.001425360554560575</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001408104784949209</v>
+        <v>0.001408104784949227</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001215722273700656</v>
+        <v>0.001215722273700666</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001446324673310548</v>
+        <v>0.001446324673310578</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001420932932350056</v>
+        <v>0.001420932932350031</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00161119326495347</v>
+        <v>0.001611193264953469</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001246009827539016</v>
+        <v>0.001246009827538985</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001933696439910295</v>
+        <v>0.001933696439910327</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001274527204967672</v>
+        <v>0.00127452720496772</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001611128320134545</v>
+        <v>0.001611128320134529</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001866754418601173</v>
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02860021321862726</v>
+        <v>0.02860021321862745</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02873477185780855</v>
+        <v>0.02873477185780864</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03270151941347197</v>
+        <v>0.03270151941347194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03361696768148782</v>
+        <v>0.03361696768148794</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06465000525460644</v>
+        <v>0.06465000525460649</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03178739692066532</v>
+        <v>0.03178739692066529</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04137137348516157</v>
+        <v>0.04137137348516159</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04583620566124466</v>
+        <v>0.04583620566124475</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04129680248033426</v>
+        <v>0.04129680248033429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04161420798563362</v>
+        <v>0.04161420798563372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03981992606823509</v>
+        <v>0.03981992606823496</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04325798957873299</v>
+        <v>0.04325798957873301</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0311641303227131</v>
+        <v>0.03116413032271302</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06931878177823758</v>
+        <v>0.06931878177823757</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04730768759599873</v>
+        <v>0.0473076875959986</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06373646584967646</v>
+        <v>0.06373646584967638</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04231837327554334</v>
+        <v>0.04231837327554336</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03903703591925345</v>
+        <v>0.03903703591925343</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05698300462454058</v>
+        <v>0.05698300462454051</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03351009637279301</v>
+        <v>0.03351009637279297</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05537641769988733</v>
+        <v>0.05537641769988735</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05415556572114341</v>
+        <v>0.05415556572114354</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03209564759696198</v>
+        <v>0.03209564759696196</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03500816609032081</v>
+        <v>0.03500816609032067</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03174583952984648</v>
+        <v>0.03174583952984641</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03282287852874445</v>
+        <v>0.03282287852874455</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02873837674573124</v>
+        <v>0.02873837674573127</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02657521820759182</v>
+        <v>0.02657521820759184</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02662361316321258</v>
+        <v>0.02662361316321266</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02654373107000823</v>
+        <v>0.0265437310700083</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02683942357439012</v>
+        <v>0.02683942357439024</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02672064398364863</v>
+        <v>0.02672064398364873</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03000342025815587</v>
+        <v>0.03000342025815599</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02671000865630594</v>
+        <v>0.02671000865630606</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02660229924783257</v>
+        <v>0.02660229924783255</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02662795777663491</v>
+        <v>0.02662795777663492</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02662166825123904</v>
+        <v>0.02662166825123905</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02655154708495845</v>
+        <v>0.02655154708495853</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02663559895174619</v>
+        <v>0.02663559895174622</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04888745796359728</v>
+        <v>0.04888745796359738</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02669569161741524</v>
+        <v>0.02669569161741538</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02656258654267813</v>
+        <v>0.02656258654267807</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0268132402376635</v>
+        <v>0.02681324023766364</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02657298079188292</v>
+        <v>0.0265729807918828</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02669566794579139</v>
+        <v>0.02669566794579146</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.026731918046613</v>
+        <v>0.02673191804661298</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00300637117556955</v>
+        <v>0.00300637117556954</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003140929814750805</v>
+        <v>0.003140929814750806</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007107677370414231</v>
+        <v>0.00710767737041417</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00802312563843008</v>
+        <v>0.008023125638430099</v>
       </c>
       <c r="F6" t="n">
         <v>0.03905616321154877</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006162317696363969</v>
+        <v>0.006162317696363897</v>
       </c>
       <c r="H6" t="n">
         <v>0.01577753144210382</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02024236361818694</v>
+        <v>0.0202423636181869</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01232721302304982</v>
+        <v>0.01232721302304985</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01602036594257591</v>
+        <v>0.01602036594257595</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01422608402517728</v>
+        <v>0.01422608402517717</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01766414753567527</v>
+        <v>0.01766414753567523</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005570288279655335</v>
+        <v>0.005570288279655257</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04369370255393619</v>
+        <v>0.04369370255393616</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02168260837169734</v>
+        <v>0.02168260837169723</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03814262380661868</v>
+        <v>0.03814262380661863</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01672453123248566</v>
+        <v>0.01672453123248563</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0134431938761957</v>
+        <v>0.0134431938761956</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03138916258148282</v>
+        <v>0.0313891625814828</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007885017148491671</v>
+        <v>0.007885017148491604</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007431158161820112</v>
+        <v>0.007431158161820102</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02853048649684203</v>
+        <v>0.0285304864968421</v>
       </c>
       <c r="X6" t="n">
-        <v>0.006470568372660626</v>
+        <v>0.006470568372660521</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009414324047263053</v>
+        <v>0.009414324047262966</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.006151997486788737</v>
+        <v>0.006151997486788691</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007229036485686727</v>
+        <v>0.007229036485686757</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003144534702673495</v>
+        <v>0.003144534702673527</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000981376164534104</v>
+        <v>0.0009813761645341358</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001029771120154844</v>
+        <v>0.001029771120154843</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009498890269504849</v>
+        <v>0.000949889026950485</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001245581531332417</v>
+        <v>0.001245581531332416</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001095564759347281</v>
+        <v>0.001095564759347283</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001033830800871516</v>
+        <v>0.001033830800871531</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="M7" t="n">
         <v>0.001116166613248236</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001008457204774817</v>
+        <v>0.001008457204774734</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001002878552333555</v>
+        <v>0.001002878552333509</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009965890269376821</v>
+        <v>0.0009965890269376535</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009577050419007058</v>
+        <v>0.0009577050419006915</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001010519727444798</v>
+        <v>0.001010519727444774</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009421984255301246</v>
+        <v>0.0009421984255301351</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001070612393113901</v>
+        <v>0.001070612393113956</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009375073183767562</v>
+        <v>0.0009375073183766725</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001219398194605798</v>
+        <v>0.001219398194605789</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009791387488251671</v>
+        <v>0.0009791387488250814</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001101825902733642</v>
+        <v>0.001101825902733681</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001138076003555259</v>
+        <v>0.001138076003555258</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409464</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="S8" t="n">
         <v>0.003907744495681524</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003131078608409468</v>
+        <v>0.003131078608409465</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007356174357962622</v>
+        <v>0.007356174357962572</v>
       </c>
       <c r="C9" t="n">
-        <v>0.007965379339455013</v>
+        <v>0.007965379339455002</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01944898102676881</v>
+        <v>0.01944898102676876</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02240708709747601</v>
+        <v>0.02240708709747604</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1129262239894016</v>
+        <v>0.1129262239894014</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01675366737498319</v>
+        <v>0.0167536673749831</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04501226846614386</v>
+        <v>0.0450122684661438</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05817694082879431</v>
+        <v>0.05817694082879434</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03503940128114569</v>
+        <v>0.03503940128114566</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04572827222865659</v>
+        <v>0.04572827222865661</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04043778590415081</v>
+        <v>0.04043778590415065</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0505327205276206</v>
+        <v>0.05053272052762053</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01491594980060764</v>
+        <v>0.01491594980060762</v>
       </c>
       <c r="O9" t="n">
         <v>0.1274159197241689</v>
       </c>
       <c r="P9" t="n">
-        <v>0.06251564311246879</v>
+        <v>0.06251564311246875</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1109563178116998</v>
+        <v>0.1109563178116999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04780452167437362</v>
+        <v>0.04780452167437357</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0381294141891963</v>
+        <v>0.03812941418919627</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09104356390819852</v>
+        <v>0.09104356390819855</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02183309096184552</v>
+        <v>0.02183309096184544</v>
       </c>
       <c r="V9" t="n">
         <v>0.02077221079127126</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08270678767100322</v>
+        <v>0.08270678767100302</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01766255241230855</v>
+        <v>0.01766255241230844</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02625018800600862</v>
+        <v>0.02625018800600872</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01663113434063816</v>
+        <v>0.01663113434063815</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01980681149559173</v>
+        <v>0.01980681149559179</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.008027651694033593</v>
+        <v>0.008027651694033638</v>
       </c>
     </row>
     <row r="10">
@@ -7197,82 +7197,82 @@
         <v>0.001385424550369677</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="E10" t="n">
         <v>0.001551467253031854</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001440752636713062</v>
+        <v>0.001440752636713063</v>
       </c>
       <c r="G10" t="n">
         <v>0.001814216186733356</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00174057369753457</v>
+        <v>0.001740573697534571</v>
       </c>
       <c r="N10" t="n">
         <v>0.001465273693170273</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001540928524453757</v>
+        <v>0.001540928524453756</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001522383697260302</v>
+        <v>0.001522383697260301</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001315629637227348</v>
+        <v>0.001315629637227349</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001563458725553828</v>
+        <v>0.001563458725553826</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001639346322078884</v>
+        <v>0.001639346322078883</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00174064349392422</v>
+        <v>0.001740643493924219</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001348179761892564</v>
+        <v>0.001348179761892565</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002087238620285236</v>
+        <v>0.002087238620285235</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001378827472677717</v>
+        <v>0.001378827472677718</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001740573697533144</v>
+        <v>0.001740573697533145</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.002111556678284522</v>
+        <v>0.002111556678284521</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="J11" t="n">
         <v>0.02687048454835291</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02437530151647923</v>
+        <v>0.02437530151647933</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04318773487132007</v>
+        <v>0.04318773487132022</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02399355047942887</v>
+        <v>0.02399355047942894</v>
       </c>
     </row>
     <row r="12">
@@ -7373,82 +7373,82 @@
         <v>0.02607029249998332</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02636973224269921</v>
+        <v>0.02636973224269927</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03201421454203559</v>
+        <v>0.03201421454203572</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0334681989112525</v>
+        <v>0.03346819891125254</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07796065692659117</v>
+        <v>0.07796065692659124</v>
       </c>
       <c r="G12" t="n">
         <v>0.0306893993304918</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04457922048645138</v>
+        <v>0.04457922048645148</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0510499917784958</v>
+        <v>0.05104999177849586</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04255423668743487</v>
+        <v>0.04255423668743495</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04493115454632264</v>
+        <v>0.04493115454632275</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04233074596139725</v>
+        <v>0.04233074596139729</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04729266307996832</v>
+        <v>0.04729266307996836</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02978611440280212</v>
+        <v>0.02978611440280216</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08508271090622509</v>
+        <v>0.08508271090622516</v>
       </c>
       <c r="P12" t="n">
         <v>0.05318257430000092</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0769923979383267</v>
+        <v>0.07699239793832677</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04595168395551526</v>
+        <v>0.04595168395551524</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0411961225531557</v>
+        <v>0.04119612255315574</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06720477294054208</v>
+        <v>0.06720477294054217</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03318606521176746</v>
+        <v>0.03318606521176751</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05185880001775604</v>
+        <v>0.05185880001775598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0631070353852277</v>
+        <v>0.06310703538522755</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03113613944261027</v>
+        <v>0.03113613944261033</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03535718075191836</v>
+        <v>0.0353571807519184</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.03062917122764767</v>
+        <v>0.03062917122764771</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03219009731840056</v>
+        <v>0.0321900973184007</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.02640034068878846</v>
+        <v>0.02640034068878858</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0231355171115304</v>
+        <v>0.02313551711153042</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0232171313229625</v>
+        <v>0.02321713132296258</v>
       </c>
       <c r="F13" t="n">
         <v>0.02316271227316392</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02334627910654388</v>
+        <v>0.02334627910654395</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02618701601902797</v>
+        <v>0.02618701601902798</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02331008195010464</v>
+        <v>0.0233100819501047</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02317476499607282</v>
+        <v>0.02317476499607286</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02321195126982796</v>
+        <v>0.02321195126982799</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02320283601559954</v>
+        <v>0.02320283601559961</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02310121113658087</v>
+        <v>0.02310121113658092</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0232230254366941</v>
+        <v>0.02322302543669414</v>
       </c>
       <c r="V13" t="n">
-        <v>0.04245451051237682</v>
+        <v>0.04245451051237686</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02331011625680533</v>
+        <v>0.02331011625680536</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02311721035072262</v>
+        <v>0.02311721035072263</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02348047657659437</v>
+        <v>0.02348047657659445</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02313227448005699</v>
+        <v>0.023132274480057</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02331008195010391</v>
+        <v>0.02331008195010401</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02349242952059827</v>
+        <v>0.02349242952059835</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001959247034835799</v>
+        <v>0.001959247034835798</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001960328907521105</v>
+        <v>0.001960328907521099</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001959247034835799</v>
+        <v>0.001959247034835798</v>
       </c>
       <c r="P14" t="n">
-        <v>0.001959247034835799</v>
+        <v>0.001959247034835798</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="S14" t="n">
-        <v>0.002367858068073932</v>
+        <v>0.002367858068073934</v>
       </c>
       <c r="T14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0019592470348358</v>
+        <v>0.001959247034835798</v>
       </c>
       <c r="V14" t="n">
         <v>0.001960919994216477</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001959247034835799</v>
+        <v>0.001959247034835798</v>
       </c>
       <c r="X14" t="n">
-        <v>0.001959247034835799</v>
+        <v>0.001959247034835798</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.001986107031023554</v>
+        <v>0.001986107031023552</v>
       </c>
     </row>
     <row r="15">
@@ -7634,13 +7634,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004062849051577977</v>
+        <v>0.00406284905157796</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00436228879429389</v>
+        <v>0.004362288794293895</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01000677109363029</v>
+        <v>0.01000677109363027</v>
       </c>
       <c r="E15" t="n">
         <v>0.01146075546284714</v>
@@ -7649,70 +7649,70 @@
         <v>0.05595321347818585</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008655095885898708</v>
+        <v>0.008655095885898663</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02257177703804609</v>
+        <v>0.0225717770380461</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02904254833009047</v>
+        <v>0.02904254833009054</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01764408104660313</v>
+        <v>0.01764408104660312</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02292371109791737</v>
+        <v>0.02292371109791741</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02032330251299201</v>
+        <v>0.02032330251299193</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02528521963156306</v>
+        <v>0.02528521963156302</v>
       </c>
       <c r="N15" t="n">
-        <v>0.007778670954396816</v>
+        <v>0.00777867095439679</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06304840746163201</v>
+        <v>0.06304840746163205</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0311482708554078</v>
+        <v>0.03114827085540774</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05498495448992135</v>
+        <v>0.05498495448992127</v>
       </c>
       <c r="R15" t="n">
-        <v>0.02394424050710988</v>
+        <v>0.02394424050710992</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01918867910475037</v>
+        <v>0.01918867910475039</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04519732949213678</v>
+        <v>0.04519732949213676</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01115176176717438</v>
+        <v>0.01115176176717439</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01063198514065219</v>
+        <v>0.01063198514065217</v>
       </c>
       <c r="W15" t="n">
-        <v>0.04107273194063464</v>
+        <v>0.04107273194063444</v>
       </c>
       <c r="X15" t="n">
-        <v>0.009101835998017206</v>
+        <v>0.009101835998017203</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01334973730351301</v>
+        <v>0.01334973730351299</v>
       </c>
       <c r="Z15" t="n">
         <v>0.008621727779242333</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01018265386999526</v>
+        <v>0.01018265386999529</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.004392897240383209</v>
+        <v>0.004392897240383183</v>
       </c>
     </row>
     <row r="16">
@@ -7722,43 +7722,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00112807366312509</v>
+        <v>0.001128073663125092</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001209687874557205</v>
+        <v>0.001209687874557207</v>
       </c>
       <c r="F16" t="n">
         <v>0.001155268824758606</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001311975661950802</v>
+        <v>0.001311975661950803</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001276860378196166</v>
+        <v>0.001276860378196165</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001302638501699319</v>
+        <v>0.00130263850169932</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001167321547667539</v>
+        <v>0.001167321547667538</v>
       </c>
       <c r="O16" t="n">
         <v>0.001177647825234877</v>
@@ -7770,37 +7770,37 @@
         <v>0.00109376768817554</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="T16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="U16" t="n">
-        <v>0.001188721992101037</v>
+        <v>0.001188721992101038</v>
       </c>
       <c r="V16" t="n">
         <v>0.001227695635273114</v>
       </c>
       <c r="W16" t="n">
-        <v>0.001275812812212253</v>
+        <v>0.001275812812212252</v>
       </c>
       <c r="X16" t="n">
-        <v>0.001082906906129545</v>
+        <v>0.001082906906129546</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.001473033128189074</v>
+        <v>0.001473033128189072</v>
       </c>
       <c r="Z16" t="n">
         <v>0.001124831031651661</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.001302638501698617</v>
+        <v>0.001302638501698618</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001484986072192943</v>
+        <v>0.001484986072192942</v>
       </c>
     </row>
   </sheetData>
@@ -9493,7 +9493,7 @@
         <v>0.005693039844583163</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00726418763899413</v>
+        <v>0.007264187638994131</v>
       </c>
       <c r="T2" t="n">
         <v>0.08251150707921519</v>
@@ -9563,7 +9563,7 @@
         <v>0.002380712257203326</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002461296928480053</v>
+        <v>0.002461296928480054</v>
       </c>
       <c r="N3" t="n">
         <v>0.002011287694561998</v>
@@ -9627,7 +9627,7 @@
         <v>0.02971484492044299</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04360242755429517</v>
+        <v>0.04360242755429516</v>
       </c>
       <c r="F4" t="n">
         <v>0.05408427526730217</v>
@@ -9681,7 +9681,7 @@
         <v>0.07407614421193359</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06883623566801184</v>
+        <v>0.06883623566801182</v>
       </c>
       <c r="X4" t="n">
         <v>0.056838551443419</v>
@@ -9748,7 +9748,7 @@
         <v>0.02888767444577995</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02887860405741651</v>
+        <v>0.02887860405741652</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02877747938264453</v>
@@ -9812,7 +9812,7 @@
         <v>0.01823925428609312</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006075750376821294</v>
+        <v>0.006075750376821295</v>
       </c>
       <c r="I6" t="n">
         <v>0.004337297033965756</v>
@@ -9869,7 +9869,7 @@
         <v>0.01322011462528831</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006245594228619674</v>
+        <v>0.006245594228619675</v>
       </c>
       <c r="AB6" t="n">
         <v>0.03048515027423655</v>
@@ -9906,7 +9906,7 @@
         <v>0.001636604884506866</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001576195774486253</v>
+        <v>0.001576195774486252</v>
       </c>
       <c r="K7" t="n">
         <v>0.001636604884506866</v>
@@ -10033,7 +10033,7 @@
         <v>0.005158371243312652</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00515837124331265</v>
+        <v>0.005158371243312651</v>
       </c>
       <c r="X8" t="n">
         <v>0.005158371243312653</v>
@@ -10085,7 +10085,7 @@
         <v>0.06180542470603429</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0074031609841911</v>
+        <v>0.007403160984191099</v>
       </c>
       <c r="L9" t="n">
         <v>0.004334902737011527</v>
@@ -10161,7 +10161,7 @@
         <v>0.002174031435031215</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0027126188831467</v>
+        <v>0.002712618883146699</v>
       </c>
       <c r="H10" t="n">
         <v>0.002606415960966251</v>
@@ -10224,7 +10224,7 @@
         <v>0.002606415960966251</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.003141426076371686</v>
+        <v>0.003141426076371685</v>
       </c>
     </row>
     <row r="11">
@@ -10285,7 +10285,7 @@
         <v>0.02673734188315316</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02533475442300964</v>
+        <v>0.02533475442300963</v>
       </c>
       <c r="T11" t="n">
         <v>0.02673734188315316</v>
@@ -10334,7 +10334,7 @@
         <v>0.0468064807997011</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06174399604685827</v>
+        <v>0.06174399604685828</v>
       </c>
       <c r="G12" t="n">
         <v>0.04959614590017676</v>
@@ -10349,7 +10349,7 @@
         <v>0.05765050924853622</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02784071313401413</v>
+        <v>0.02784071313401412</v>
       </c>
       <c r="L12" t="n">
         <v>0.02633258616848811</v>
@@ -10376,7 +10376,7 @@
         <v>0.02806265680870807</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06781159076826397</v>
+        <v>0.06781159076826399</v>
       </c>
       <c r="U12" t="n">
         <v>0.06257234603706258</v>
@@ -10391,13 +10391,13 @@
         <v>0.06584999011474871</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08451080958477228</v>
+        <v>0.08451080958477229</v>
       </c>
       <c r="Z12" t="n">
         <v>0.04227068629081884</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03216268568101014</v>
+        <v>0.03216268568101015</v>
       </c>
       <c r="AB12" t="n">
         <v>0.06711933936557769</v>
@@ -10425,7 +10425,7 @@
         <v>0.02527046296469849</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0255351923936974</v>
+        <v>0.02553519239369741</v>
       </c>
       <c r="H13" t="n">
         <v>0.02548299095631675</v>
@@ -10482,7 +10482,7 @@
         <v>0.02573208707567385</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0252265673467053</v>
+        <v>0.02522656734670529</v>
       </c>
       <c r="AA13" t="n">
         <v>0.02548299095631675</v>
@@ -10549,7 +10549,7 @@
         <v>0.003220929343701961</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001818341883558449</v>
+        <v>0.00181834188355845</v>
       </c>
       <c r="T14" t="n">
         <v>0.003220929343701961</v>
@@ -10613,7 +10613,7 @@
         <v>0.03103522542139047</v>
       </c>
       <c r="K15" t="n">
-        <v>0.004324300594562921</v>
+        <v>0.004324300594562922</v>
       </c>
       <c r="L15" t="n">
         <v>0.002816173629036892</v>
@@ -10640,7 +10640,7 @@
         <v>0.004546244269256887</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04429517822881276</v>
+        <v>0.04429517822881275</v>
       </c>
       <c r="U15" t="n">
         <v>0.03902547040226163</v>
@@ -10649,7 +10649,7 @@
         <v>0.03287674847385755</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05969106269161296</v>
+        <v>0.05969106269161295</v>
       </c>
       <c r="X15" t="n">
         <v>0.04230311447994781</v>
@@ -10746,7 +10746,7 @@
         <v>0.002215674536222625</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001710154807254036</v>
+        <v>0.001710154807254035</v>
       </c>
       <c r="AA16" t="n">
         <v>0.00196657841686555</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide ionising radiation results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide ionising radiation results.xlsx
@@ -586,82 +586,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004199064778191686</v>
+        <v>0.004199064778191499</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009164483059376732</v>
+        <v>0.009164483059376725</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01270109596820659</v>
+        <v>0.01270109596820647</v>
       </c>
       <c r="E2" t="n">
         <v>0.1240501027730405</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02080068612801483</v>
+        <v>0.02080068612801481</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02161330648832532</v>
+        <v>0.0216133064883252</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0459833569251578</v>
+        <v>0.04598335692515765</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01607337904496084</v>
+        <v>0.01607337904496094</v>
       </c>
       <c r="J2" t="n">
         <v>0.04893511810186368</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03641398215732194</v>
+        <v>0.03641398215732172</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006236427836030345</v>
+        <v>0.006236427836030165</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03882196202277052</v>
+        <v>0.03882196202277051</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02709070543803313</v>
+        <v>0.02709070543803295</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04710026966412627</v>
+        <v>0.04710026966412613</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09381937009914453</v>
+        <v>0.09381937009914441</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02577664366799605</v>
+        <v>0.02577664366799596</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02851048144035569</v>
+        <v>0.02851048144035556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004681161696151698</v>
+        <v>0.004681161696151592</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06391477752511424</v>
+        <v>0.06391477752511412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05446063966374914</v>
+        <v>0.05446063966374904</v>
       </c>
       <c r="V2" t="n">
-        <v>0.07410111363787732</v>
+        <v>0.07410111363787725</v>
       </c>
       <c r="W2" t="n">
         <v>0.1349065761945482</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004477847984904523</v>
+        <v>0.004477847984904381</v>
       </c>
       <c r="Y2" t="n">
         <v>0.1252784391812158</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08201316105802062</v>
+        <v>0.08201316105802058</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01348163421951902</v>
+        <v>0.01348163421951889</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01178035093628358</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002051956309815374</v>
+        <v>0.002051956309815508</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002348847811213074</v>
+        <v>0.00234884781121307</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002249156891728384</v>
+        <v>0.00224915689172838</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001945328828438328</v>
+        <v>0.001945328828438325</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002643581900186614</v>
+        <v>0.002643581900186463</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002476458957041862</v>
+        <v>0.002476458957041728</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002399919603682471</v>
+        <v>0.002399919603682467</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002162128226064986</v>
+        <v>0.002162128226064995</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002266513037765873</v>
+        <v>0.002266513037765413</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002240925798172592</v>
+        <v>0.002240925798172391</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001955656724677204</v>
+        <v>0.001955656724677072</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002304039199867424</v>
+        <v>0.002304039199867651</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002270162234163402</v>
+        <v>0.002270162234163401</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002542069920638256</v>
+        <v>0.002542069920638098</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002000567784242001</v>
+        <v>0.002000567784242074</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003031301950067457</v>
+        <v>0.003031301950067459</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002042853986790733</v>
+        <v>0.002042853986790707</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002541973619016356</v>
+        <v>0.00254197361901618</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00284277883650217</v>
+        <v>0.002842778836502167</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02942339093152327</v>
+        <v>0.02942339093152309</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03111049386947327</v>
+        <v>0.03111049386947312</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03252228146439296</v>
+        <v>0.03252228146439278</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07308741602294938</v>
+        <v>0.07308741602294935</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0353582096392786</v>
+        <v>0.03535820963927849</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03577067754651665</v>
+        <v>0.03577067754651645</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04465327476316191</v>
+        <v>0.04465327476316166</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03375143904652271</v>
+        <v>0.03375143904652252</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0494665566277198</v>
+        <v>0.04946655662771976</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04116535002955751</v>
+        <v>0.04116535002955727</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03016598584218056</v>
+        <v>0.03016598584218034</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04195275341975912</v>
+        <v>0.04195275341975899</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03776712514481938</v>
+        <v>0.03776712514481947</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04506037634106437</v>
+        <v>0.04506037634106412</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06208893984625337</v>
+        <v>0.06208893984625313</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0372881650601332</v>
+        <v>0.03728816506013299</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03828461682581434</v>
+        <v>0.03828461682581418</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02959910959705184</v>
+        <v>0.02959910959705167</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05118906701047449</v>
+        <v>0.05118906701047428</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04774314477609869</v>
+        <v>0.04774314477609848</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08002614527028891</v>
+        <v>0.08002614527028884</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07706474399769515</v>
+        <v>0.07706474399769503</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02952500413673239</v>
+        <v>0.02952500413673206</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07355540111562844</v>
+        <v>0.07355540111562794</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05778571528626964</v>
+        <v>0.05778571528626945</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03280677849145345</v>
+        <v>0.03280677849145324</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03205255034366595</v>
+        <v>0.03205255034366583</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02864079510742071</v>
+        <v>0.0286407951074205</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02862627485474737</v>
+        <v>0.02862627485474727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02869240150812839</v>
+        <v>0.02869240150812826</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02848565331436695</v>
+        <v>0.02848565331436684</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02885643568789255</v>
+        <v>0.02885643568789236</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03253292091455134</v>
+        <v>0.03253292091455137</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0286773466472167</v>
+        <v>0.02867734664721656</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02868095147718968</v>
+        <v>0.02868095147718937</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02871899851530632</v>
+        <v>0.02871899851530601</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02870967226693514</v>
+        <v>0.0287096722669348</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02860569503944462</v>
+        <v>0.02860569503944468</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0287326763607379</v>
+        <v>0.02873267636073771</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05384460696525217</v>
+        <v>0.0538446069652521</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02881943576336103</v>
+        <v>0.02881943576336089</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02862206459328369</v>
+        <v>0.02862206459328335</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02899775509323542</v>
+        <v>0.02899775509323515</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02863747741756308</v>
+        <v>0.02863747741756294</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02881940066255065</v>
+        <v>0.0288194006625506</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02879491026356592</v>
+        <v>0.02879491026356576</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002384805749043963</v>
+        <v>0.002384805749043898</v>
       </c>
       <c r="C6" t="n">
         <v>0.004071908686993946</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00548369628191368</v>
+        <v>0.005483696281913569</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04604883084047009</v>
+        <v>0.04604883084047013</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008319624456799308</v>
+        <v>0.008319624456799304</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008691726344202729</v>
+        <v>0.008691726344202625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01761468958068257</v>
+        <v>0.01761468958068247</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00671285386404342</v>
+        <v>0.006712853864043361</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0186102839188259</v>
+        <v>0.01861028391882581</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01412676484707817</v>
+        <v>0.01412676484707807</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00312740065970125</v>
+        <v>0.00312740065970114</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01491416823727978</v>
+        <v>0.0149141682372798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01072853996234004</v>
+        <v>0.01072853996234031</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01798142513875042</v>
+        <v>0.01798142513875031</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03500998864393946</v>
+        <v>0.03500998864393936</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0102495798776539</v>
+        <v>0.01024957987765379</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01124603164333507</v>
+        <v>0.01124603164333497</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002560524414572569</v>
+        <v>0.002560524414572477</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02415048182799518</v>
+        <v>0.02415048182799511</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02066419357378474</v>
+        <v>0.02066419357378465</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02773715681843051</v>
+        <v>0.02773715681843045</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04998579279538124</v>
+        <v>0.04998579279538121</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002446052934418492</v>
+        <v>0.002446052934418268</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04651681593314914</v>
+        <v>0.0465168159331488</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03074713010379037</v>
+        <v>0.0307471301037903</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005768193308974149</v>
+        <v>0.00576819330897406</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.005013965161186634</v>
+        <v>0.00501396516118663</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001602209924941368</v>
+        <v>0.001602209924941292</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001587689672268088</v>
+        <v>0.001587689672268085</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001653816325649087</v>
+        <v>0.001653816325649085</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001447068131887644</v>
+        <v>0.001447068131887641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001777484485578638</v>
+        <v>0.001777484485578543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001676648205657431</v>
+        <v>0.001676648205657473</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001638761464737394</v>
+        <v>0.001638761464737391</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001642366294710394</v>
+        <v>0.001642366294710187</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001640047312992406</v>
+        <v>0.001640047312992189</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001630721064621192</v>
+        <v>0.00163072106462099</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001567109856965324</v>
+        <v>0.001567109856965481</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001653725158423979</v>
+        <v>0.001653725158423901</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001555618513393734</v>
+        <v>0.001555618513393731</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001740484561047106</v>
+        <v>0.001740484561047072</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001543113390969791</v>
+        <v>0.00154311339096952</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001959169910756131</v>
+        <v>0.001959169910755966</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00159889223508376</v>
+        <v>0.001598892235083739</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001780815480071371</v>
+        <v>0.001780815480071424</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001756325081086614</v>
+        <v>0.001756325081086611</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001878745461394355</v>
+        <v>0.00187874546139397</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007003823888635179</v>
+        <v>0.007003823888635189</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006414012366468702</v>
+        <v>0.006414012366468286</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02522394753387914</v>
+        <v>0.02522394753387911</v>
       </c>
       <c r="F2" t="n">
         <v>0.1335798071435792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05759324609254158</v>
+        <v>0.05759324609254125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03416523004719881</v>
+        <v>0.03416523004719843</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02175070644508498</v>
+        <v>0.0217507064450846</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05741678436256842</v>
+        <v>0.05741678436256829</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07923164878434209</v>
+        <v>0.07923164878434165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05730039054779216</v>
+        <v>0.05730039054779151</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09506235848855953</v>
+        <v>0.09506235848855939</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0454867536350298</v>
+        <v>0.04548675363503014</v>
       </c>
       <c r="O2" t="n">
-        <v>0.204139055894574</v>
+        <v>0.2041390558945735</v>
       </c>
       <c r="P2" t="n">
         <v>0.1322533471256338</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03442933404286874</v>
+        <v>0.03442933404286837</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02248127220938955</v>
+        <v>0.02248127220938923</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07103136880795979</v>
+        <v>0.07103136880795943</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09553436637812189</v>
+        <v>0.09553436637812178</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06883493938611719</v>
+        <v>0.06883493938611669</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02026740462004547</v>
+        <v>0.02026740462004548</v>
       </c>
       <c r="W2" t="n">
-        <v>0.07387477620956333</v>
+        <v>0.0738747762095632</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06594236880713815</v>
+        <v>0.06594236880713771</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05369205947927679</v>
+        <v>0.05369205947927636</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01451605358637176</v>
+        <v>0.01451605358637174</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01764588794464885</v>
+        <v>0.01764588794464845</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04170109550042703</v>
+        <v>0.04170109550042701</v>
       </c>
     </row>
     <row r="3">
@@ -1358,82 +1358,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001789408868319226</v>
+        <v>0.001789408868318769</v>
       </c>
       <c r="C3" t="n">
         <v>0.002148118665609213</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001887224888069151</v>
+        <v>0.001887224888069152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002168747227414472</v>
+        <v>0.002168747227414469</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002337830964748091</v>
+        <v>0.002337830964748052</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0021957535221215</v>
+        <v>0.002195753522121306</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002363204890597782</v>
+        <v>0.002363204890597756</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001891535473877924</v>
+        <v>0.00189153547387767</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001988297578583161</v>
+        <v>0.001988297578583001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001964578848650022</v>
+        <v>0.00196457884864954</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001700141566065203</v>
+        <v>0.001700141566065247</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002018508140613495</v>
+        <v>0.002018508140613388</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001982192940204678</v>
+        <v>0.001982192940204676</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002243731903738551</v>
+        <v>0.002243731903738533</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001741772992955574</v>
+        <v>0.001741772992955194</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002689410813645528</v>
+        <v>0.002689410813645473</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001780971242959067</v>
+        <v>0.00178097124295889</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002243642634345963</v>
+        <v>0.002243642634346196</v>
       </c>
       <c r="AB3" t="n">
         <v>0.002712093546904378</v>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02909584994527862</v>
+        <v>0.02909584994527825</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03090317424646668</v>
+        <v>0.03090317424646686</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03074890147638544</v>
+        <v>0.03074890147638491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03753210303923066</v>
+        <v>0.03753210303923082</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0772954428469146</v>
+        <v>0.07729544284691471</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04940313119263458</v>
+        <v>0.04940313119263397</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04086389444976104</v>
+        <v>0.04086389444976065</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03633894637548673</v>
+        <v>0.03633894637548635</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05237964503698546</v>
+        <v>0.05237964503698567</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05729007488284292</v>
+        <v>0.05729007488284258</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04929638878545649</v>
+        <v>0.04929638878545633</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06313616589426882</v>
+        <v>0.06313616589426889</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04499045685348324</v>
+        <v>0.04499045685348326</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1028173580376957</v>
+        <v>0.1028173580376953</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07661586131602709</v>
+        <v>0.07661586131602723</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04096015725491701</v>
+        <v>0.04096015725491661</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03660522901783943</v>
+        <v>0.03660522901783901</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0543011691240006</v>
+        <v>0.05430116912400026</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0632322240096002</v>
+        <v>0.06323222400960024</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05350059639151548</v>
+        <v>0.05350059639151504</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05620416408620505</v>
+        <v>0.05620416408620507</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05533755773290971</v>
+        <v>0.0553375577329094</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05244628838175623</v>
+        <v>0.05244628838175586</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04798119448214556</v>
+        <v>0.04798119448214524</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03370200036206852</v>
+        <v>0.0337020003620685</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03484278823328998</v>
+        <v>0.03484278823328984</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.043606794087788</v>
+        <v>0.0436067940877881</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02906328780614553</v>
+        <v>0.02906328780614559</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02913332671124332</v>
+        <v>0.0291333267112434</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="E5" t="n">
         <v>0.02902614166846577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02939765461404616</v>
+        <v>0.02939765461404636</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02926318122039665</v>
+        <v>0.02926318122039668</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03225222773372501</v>
+        <v>0.03225222773372508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02934841293623086</v>
+        <v>0.02934841293623081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02910051175464071</v>
+        <v>0.02910051175464062</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02913578040556779</v>
+        <v>0.0291357804055677</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0291271352070266</v>
+        <v>0.02912713520702638</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02903075092270367</v>
+        <v>0.02903075092270375</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02914679180067734</v>
+        <v>0.02914679180067745</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04953941914469919</v>
+        <v>0.04953941914469917</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02922888321762563</v>
+        <v>0.02922888321762562</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02904592508894428</v>
+        <v>0.0290459250889442</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02939132794686077</v>
+        <v>0.02939132794686075</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02906021239078133</v>
+        <v>0.02906021239078148</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02922885067998024</v>
+        <v>0.02922885067998036</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02939576070770485</v>
+        <v>0.02939576070770499</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001402149964549934</v>
+        <v>0.001402149964549418</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003209474265738182</v>
+        <v>0.003209474265738185</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003055201495656763</v>
+        <v>0.003055201495656347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009838403058502131</v>
+        <v>0.009838403058502129</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04960174286618611</v>
+        <v>0.04960174286618604</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02167493033758466</v>
+        <v>0.02167493033758403</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01317019446903235</v>
+        <v>0.01317019446903184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008645246394758034</v>
+        <v>0.008645246394757524</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02158155292602109</v>
+        <v>0.02158155292602104</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02959637490211426</v>
+        <v>0.02959637490211374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02160268880472786</v>
+        <v>0.0216026888047279</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03544246591354025</v>
+        <v>0.03544246591353991</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01729675687275472</v>
+        <v>0.01729675687275448</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07508915718264579</v>
+        <v>0.07508915718264543</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04888766046097717</v>
+        <v>0.04888766046097739</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01326645727418834</v>
+        <v>0.01326645727418782</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008911529037110729</v>
+        <v>0.008911529037110092</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02660746914327202</v>
+        <v>0.02660746914327148</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03553852402887151</v>
+        <v>0.03553852402887139</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02577239553646555</v>
+        <v>0.02577239553646511</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007987358733803905</v>
+        <v>0.007987358733803919</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0276093568778598</v>
+        <v>0.02760935687785945</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02471808752670633</v>
+        <v>0.02471808752670595</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0202874945014169</v>
+        <v>0.02028749450141643</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.006008300381339835</v>
+        <v>0.006008300381339684</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007149088252561269</v>
+        <v>0.007149088252561218</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01591309410705943</v>
+        <v>0.01591309410705942</v>
       </c>
     </row>
     <row r="7">
@@ -1710,82 +1710,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001369587825416885</v>
+        <v>0.00136958782541671</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001439626730514691</v>
+        <v>0.001439626730514693</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="E7" t="n">
         <v>0.001332441687737072</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001703954633317657</v>
+        <v>0.001703954633317655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001534980365346795</v>
+        <v>0.001534980365346707</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001454135622760667</v>
+        <v>0.001454135622760463</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001654712955502188</v>
+        <v>0.001654712955501868</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001406811773912181</v>
+        <v>0.001406811773911812</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001407579550517871</v>
+        <v>0.001407579550517783</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001398934351976713</v>
+        <v>0.001398934351976439</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001337050941975084</v>
+        <v>0.001337050941974922</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00141859094562744</v>
+        <v>0.001418590945627536</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001322613792298026</v>
+        <v>0.001322613792298025</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001500682362575757</v>
+        <v>0.001500682362575701</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001317724233894496</v>
+        <v>0.001317724233894295</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001697627966132129</v>
+        <v>0.001697627966131883</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001366512410052758</v>
+        <v>0.001366512410052673</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001535150699251611</v>
+        <v>0.001535150699251564</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001702060726976336</v>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003040487684185153</v>
+        <v>0.003040487684185468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01247965009884324</v>
+        <v>0.01247965009884338</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005117329432258276</v>
+        <v>0.005117329432258145</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1125195736378264</v>
+        <v>0.1125195736378267</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02046594149352288</v>
+        <v>0.02046594149352292</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01742194962587688</v>
+        <v>0.01742194962587678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04603514811435355</v>
+        <v>0.04603514811435354</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02013591817127305</v>
+        <v>0.02013591817127302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04345218044085065</v>
+        <v>0.04345218044085042</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02904588405207566</v>
+        <v>0.02904588405207565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00397797889100272</v>
+        <v>0.003977978891004309</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02597183136317176</v>
+        <v>0.02597183136317169</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02051854650937056</v>
+        <v>0.02051854650937046</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1210390952044417</v>
+        <v>0.1210390952044418</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08571466464848795</v>
+        <v>0.08571466464848783</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0464671345842212</v>
+        <v>0.04646713458422103</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03642681383412391</v>
+        <v>0.03642681383412389</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004055865694553037</v>
+        <v>0.004055865694553085</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05719964810509315</v>
+        <v>0.05719964810509313</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05032840895868573</v>
+        <v>0.05032840895868562</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08248990531800299</v>
+        <v>0.08248990531800286</v>
       </c>
       <c r="W2" t="n">
-        <v>0.124553654289245</v>
+        <v>0.1245536542892449</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004732107753738046</v>
+        <v>0.004732107753738035</v>
       </c>
       <c r="Y2" t="n">
         <v>0.1271392284961958</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.07933881523274083</v>
+        <v>0.07933881523274092</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01800549269506754</v>
+        <v>0.0180054926950676</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01120050428658767</v>
+        <v>0.01120050428658769</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001971314847924403</v>
+        <v>0.00197131484792419</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002261057954629539</v>
+        <v>0.002261057954629414</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002147209919147801</v>
+        <v>0.002147209919147803</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001871830284351488</v>
+        <v>0.001871830284351491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002531874865110084</v>
+        <v>0.002531874865109997</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002380418718143968</v>
+        <v>0.002380418718143949</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002269253863405598</v>
+        <v>0.002269253863405601</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002075701764705742</v>
+        <v>0.002075701764705689</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00217460545108979</v>
+        <v>0.002174605451089506</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002150361767750787</v>
+        <v>0.00215036176775071</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001880071842243794</v>
+        <v>0.001880071842243575</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002210792264367493</v>
+        <v>0.002210792264367308</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002199540875663325</v>
+        <v>0.002199540875663429</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002435693161824449</v>
+        <v>0.002435693161824396</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001922624674198293</v>
+        <v>0.001922624674198215</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002900315824557455</v>
+        <v>0.002900315824557255</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001962690477317122</v>
+        <v>0.001962690477316903</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002435601916873348</v>
+        <v>0.002435601916873289</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00271999853299606</v>
+        <v>0.002719998532996058</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0286427169833254</v>
+        <v>0.02864271698332529</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03197225610562252</v>
+        <v>0.03197225610562253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02939970141299098</v>
+        <v>0.0293997014129909</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06852039242861489</v>
+        <v>0.06852039242861498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03488489978699087</v>
+        <v>0.03488489978699084</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03388459098541975</v>
+        <v>0.0338845909854197</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04431376584132926</v>
+        <v>0.04431376584132922</v>
       </c>
       <c r="I4" t="n">
-        <v>0.034873800651189</v>
+        <v>0.03487380065118894</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04724290146823132</v>
+        <v>0.04724290146823117</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03812137858863984</v>
+        <v>0.0381213785886398</v>
       </c>
       <c r="L4" t="n">
         <v>0.02898442151963296</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03689520633954716</v>
+        <v>0.03689520633954712</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0350132641873768</v>
+        <v>0.03501326418737667</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07165182381485315</v>
+        <v>0.07165182381485297</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0587764836776139</v>
+        <v>0.05877648367761372</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04447121983695472</v>
+        <v>0.04447121983695474</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04081164082294308</v>
+        <v>0.040811640822943</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02901281034493394</v>
+        <v>0.02901281034493387</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04838309498777602</v>
+        <v>0.04838309498777593</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04587860900507421</v>
+        <v>0.04587860900507415</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08358808332491681</v>
+        <v>0.08358808332491689</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07293283933122736</v>
+        <v>0.07293283933122728</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02925929263467174</v>
+        <v>0.02925929263467187</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07387525076831579</v>
+        <v>0.07387525076831572</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0564525614345778</v>
+        <v>0.05645256143457775</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0340972855818311</v>
+        <v>0.03409728558183107</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03148946988309031</v>
+        <v>0.03148946988309028</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02825301603936968</v>
+        <v>0.02825301603936961</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02824769926182379</v>
+        <v>0.02824769926182355</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02829096191088646</v>
+        <v>0.02829096191088643</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02810756459432543</v>
+        <v>0.02810756459432538</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02845733358320582</v>
+        <v>0.02845733358320565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0322727266092806</v>
+        <v>0.03227272660928052</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0282558951705997</v>
+        <v>0.02825589517059964</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02829106384476342</v>
+        <v>0.02829106384476329</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02832711307706465</v>
+        <v>0.02832711307706446</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02831827653917134</v>
+        <v>0.0283182765391711</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02821975903522857</v>
+        <v>0.0282197590352285</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02834030274557737</v>
+        <v>0.02834030274557723</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05432318830274407</v>
+        <v>0.05432318830274411</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02842227648178077</v>
+        <v>0.02842227648178069</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02823526904279542</v>
+        <v>0.02823526904279535</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02859162598647218</v>
+        <v>0.0285916259864719</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02824987255755581</v>
+        <v>0.0282498725575557</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02842224322406756</v>
+        <v>0.0284222432240673</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02839842511903246</v>
+        <v>0.02839842511903243</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001935965066853619</v>
+        <v>0.001935965066853433</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005265504189150741</v>
+        <v>0.005265504189150441</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002692949496519207</v>
+        <v>0.002692949496519022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04181364051214302</v>
+        <v>0.04181364051214318</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008178147870519141</v>
+        <v>0.008178147870519136</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007138512622868483</v>
+        <v>0.007138512622868423</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01760701392485751</v>
+        <v>0.01760701392485736</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008167048734717242</v>
+        <v>0.008167048734717077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01659285644100704</v>
+        <v>0.01659285644100691</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01141462667216805</v>
+        <v>0.01141462667216792</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002277669603161166</v>
+        <v>0.002277669603161057</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01018845442307541</v>
+        <v>0.0101884544230754</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008306512270904986</v>
+        <v>0.008306512270904825</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04490574545230173</v>
+        <v>0.04490574545230168</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03203040531506255</v>
+        <v>0.03203040531506243</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01776446792048303</v>
+        <v>0.01776446792048279</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0141048889064713</v>
+        <v>0.01410488890647114</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002306058428462153</v>
+        <v>0.002306058428462004</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02167634307130423</v>
+        <v>0.02167634307130407</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01913253064252293</v>
+        <v>0.01913253064252292</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03078711961354116</v>
+        <v>0.03078711961354108</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0461867609686761</v>
+        <v>0.04618676096867607</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002513214272120438</v>
+        <v>0.002513214272120508</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04716849885184398</v>
+        <v>0.04716849885184379</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02974580951810604</v>
+        <v>0.02974580951810597</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007390533665359308</v>
+        <v>0.007390533665359185</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004782717966618544</v>
+        <v>0.004782717966618552</v>
       </c>
     </row>
     <row r="7">
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001546264122897914</v>
+        <v>0.001546264122897707</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001540947345351979</v>
+        <v>0.001540947345351637</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="E7" t="n">
         <v>0.001584209994414706</v>
@@ -2409,70 +2409,70 @@
         <v>0.001400812677853651</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001711255220654531</v>
+        <v>0.001711255220654406</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001622681582056361</v>
+        <v>0.001622681582056304</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001549143254127919</v>
+        <v>0.001549143254127921</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001584311928291644</v>
+        <v>0.001584311928291465</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001581034714513408</v>
+        <v>0.001581034714513221</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001572198176620048</v>
+        <v>0.001572198176619871</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001513007118756797</v>
+        <v>0.001513007118756548</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00159422438302611</v>
+        <v>0.001594224383025999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00152222459136849</v>
+        <v>0.001522224591368539</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001676198119229489</v>
+        <v>0.001676198119229451</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001489190680244137</v>
+        <v>0.001489190680244124</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001884874070000428</v>
+        <v>0.001884874070000272</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001543120641084043</v>
+        <v>0.001543120641083905</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001715491307595788</v>
+        <v>0.001715491307595727</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001691673202560694</v>
+        <v>0.001691673202560697</v>
       </c>
     </row>
   </sheetData>
@@ -2638,82 +2638,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004946505594303569</v>
+        <v>0.00494650559430385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009961143896426767</v>
+        <v>0.009961143896426772</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005827916861913864</v>
+        <v>0.005827916861914095</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06294268921733008</v>
+        <v>0.06294268921733001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07319715106836071</v>
+        <v>0.07319715106836079</v>
       </c>
       <c r="G2" t="n">
         <v>0.01401128858071822</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04341386845059297</v>
+        <v>0.04341386845059303</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01354046155811498</v>
+        <v>0.01354046155811495</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03403557992406913</v>
+        <v>0.03403557992406917</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00533395187011635</v>
+        <v>0.005333951870116331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002449993565282746</v>
+        <v>0.002449993565282788</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02184446579567142</v>
+        <v>0.0218444657956714</v>
       </c>
       <c r="N2" t="n">
         <v>0.01736409690763138</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1640575619134154</v>
+        <v>0.1640575619134153</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07763168779780981</v>
+        <v>0.07763168779780984</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08680025714224514</v>
+        <v>0.08680025714224522</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03263918456568218</v>
+        <v>0.03263918456568216</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003273888527688193</v>
+        <v>0.003273888527688245</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0759160227789025</v>
+        <v>0.07591602277890259</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04112197083261321</v>
+        <v>0.04112197083261311</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06201274897218397</v>
+        <v>0.0620127489721841</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1020927914140173</v>
+        <v>0.102092791414017</v>
       </c>
       <c r="X2" t="n">
-        <v>0.006455669961181401</v>
+        <v>0.006455669961181398</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09233777158602303</v>
+        <v>0.09233777158602326</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04829354605410846</v>
+        <v>0.04829354605410845</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01719768232334639</v>
+        <v>0.01719768232334636</v>
       </c>
       <c r="AB2" t="n">
         <v>0.008940032953289816</v>
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001633705217703371</v>
+        <v>0.001633705217703433</v>
       </c>
       <c r="C3" t="n">
         <v>0.001899440661221611</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001743411502596111</v>
+        <v>0.001743411502596112</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001765657323874905</v>
+        <v>0.001765657323874907</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002105113494428499</v>
+        <v>0.002105113494428538</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001983104641478194</v>
+        <v>0.001983104641478285</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001905882793438797</v>
+        <v>0.001905882793438799</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001721490387969478</v>
+        <v>0.001721490387969516</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001804664383493521</v>
+        <v>0.001804664383493637</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001784276427459327</v>
+        <v>0.001784276427459375</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001556973544462524</v>
+        <v>0.001556973544462628</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001833823744020863</v>
+        <v>0.00183382374402107</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001832795875332896</v>
+        <v>0.001832795875332946</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002024228576475233</v>
+        <v>0.002024228576475311</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001592758753122614</v>
+        <v>0.001592758753122681</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002412780914633083</v>
+        <v>0.002412780914633016</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001626452471234659</v>
+        <v>0.001626452471234675</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00202415184316521</v>
+        <v>0.002024151843165229</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002284422722242141</v>
+        <v>0.002284422722242125</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02857948269436162</v>
+        <v>0.02857948269436165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03032800405007171</v>
+        <v>0.03032800405007178</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02890074675135181</v>
+        <v>0.02890074675135192</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04967212054043896</v>
+        <v>0.04967212054043903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0535012423569795</v>
+        <v>0.0535012423569796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03188348964885372</v>
+        <v>0.03188348964885374</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04260038474889864</v>
+        <v>0.04260038474889866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03171187872784484</v>
+        <v>0.03171187872784485</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04290910361321701</v>
+        <v>0.04290910361321713</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02872070231227138</v>
+        <v>0.02872070231227141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0276695333753077</v>
+        <v>0.02766953337530778</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03466342939200649</v>
+        <v>0.03466342939200652</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03310554891335044</v>
+        <v>0.03310554891335048</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0865735943463241</v>
+        <v>0.08657359434632414</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05507237809503806</v>
+        <v>0.05507237809503811</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05841421395830781</v>
+        <v>0.0584142139583079</v>
       </c>
       <c r="R4" t="n">
         <v>0.03867313899557467</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02796983341444143</v>
+        <v>0.02796983341444144</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05444703834200212</v>
+        <v>0.05444703834200223</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04176501497996557</v>
+        <v>0.0417650149799656</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07436510915418883</v>
+        <v>0.0743651091541891</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0639881631263651</v>
+        <v>0.06398816312636509</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02912955538458564</v>
+        <v>0.02912955538458578</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06043257294828733</v>
+        <v>0.06043257294828742</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04437896993531273</v>
+        <v>0.0443789699353127</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03304489275151724</v>
+        <v>0.03304489275151728</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0299412856217343</v>
+        <v>0.02994128562173438</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02737200585795678</v>
+        <v>0.02737200585795685</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02738960788613826</v>
+        <v>0.0273896078861383</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02736570245161988</v>
+        <v>0.02736570245161989</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02746530167806275</v>
+        <v>0.02746530167806283</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0275438286392676</v>
+        <v>0.02754382863926778</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03122635275188001</v>
+        <v>0.03122635275188006</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02739605001835504</v>
+        <v>0.02739605001835512</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02740400252169325</v>
+        <v>0.02740400252169342</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02743431846638346</v>
+        <v>0.02743431846638355</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0274268872958164</v>
+        <v>0.02742688729581643</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0273440380640893</v>
+        <v>0.02734403806408934</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02744494671088911</v>
+        <v>0.02744494671088922</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05243022291907408</v>
+        <v>0.052430222919074</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02751434703647233</v>
+        <v>0.02751434703647246</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02735708135243478</v>
+        <v>0.02735708135243493</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02765596980111894</v>
+        <v>0.02765596980111896</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02736936231703502</v>
+        <v>0.02736936231703505</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02751431906808186</v>
+        <v>0.02751431906808199</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0275153938466386</v>
+        <v>0.02751539384663865</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002485374013739914</v>
+        <v>0.002485374013739827</v>
       </c>
       <c r="C6" t="n">
         <v>0.004233895369450028</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002806638070730098</v>
+        <v>0.002806638070730159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0235780118598173</v>
+        <v>0.02357801185981728</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02740713367635782</v>
+        <v>0.02740713367635787</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005754666610874109</v>
+        <v>0.005754666610874057</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01650627606827691</v>
+        <v>0.01650627606827692</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005617770047223128</v>
+        <v>0.005617770047223106</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01302869595425405</v>
+        <v>0.01302869595425413</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002626593631649681</v>
+        <v>0.002626593631649667</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001575424694686009</v>
+        <v>0.001575424694686034</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008569320711384798</v>
+        <v>0.008569320711384805</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007011440232728707</v>
+        <v>0.007011440232728699</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06044477130834451</v>
+        <v>0.06044477130834448</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0289435550570585</v>
+        <v>0.02894355505705847</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03232010527768612</v>
+        <v>0.03232010527768615</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01257903031495302</v>
+        <v>0.01257903031495294</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001875724733819725</v>
+        <v>0.00187572473381972</v>
       </c>
       <c r="T6" t="n">
         <v>0.02835292966138046</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01563619194198598</v>
+        <v>0.01563619194198595</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02319908201954193</v>
+        <v>0.02319908201954201</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03785934008838555</v>
+        <v>0.03785934008838545</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003000732346606238</v>
+        <v>0.003000732346606128</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03433846426766565</v>
+        <v>0.03433846426766569</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01828486125469097</v>
+        <v>0.01828486125469091</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006950784070895531</v>
+        <v>0.006950784070895518</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003847176941112632</v>
+        <v>0.003847176941112623</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001277897177335111</v>
+        <v>0.001277897177335078</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001295499205516578</v>
+        <v>0.00129549920551658</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001271593770998196</v>
+        <v>0.001271593770998197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001371192997441078</v>
+        <v>0.00137119299744108</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001415005601288011</v>
+        <v>0.001415005601288127</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001345945092917058</v>
+        <v>0.001345945092917076</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001301941337733382</v>
+        <v>0.001301941337733383</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001309893841071549</v>
+        <v>0.001309893841071678</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001305495428403858</v>
+        <v>0.001305495428403905</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001298064257836815</v>
+        <v>0.00129806425783679</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001249929383467626</v>
+        <v>0.001249929383467616</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001316123672909523</v>
+        <v>0.001316123672909582</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001264195784427141</v>
+        <v>0.001264195784427194</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001385523998492733</v>
+        <v>0.001385523998492809</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001228258314455182</v>
+        <v>0.001228258314455267</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001561861120497244</v>
+        <v>0.001561861120497198</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001275253636413293</v>
+        <v>0.001275253636413323</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001420210387460155</v>
+        <v>0.001420210387460253</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001421285166016919</v>
+        <v>0.001421285166016908</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006836386566818235</v>
+        <v>0.006836386566817885</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007331190709214715</v>
+        <v>0.007331190709214728</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01808861791171843</v>
+        <v>0.01808861791171809</v>
       </c>
       <c r="E2" t="n">
-        <v>0.020753304026405</v>
+        <v>0.02075330402640499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1053136649322869</v>
+        <v>0.1053136649322871</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01558065647748882</v>
+        <v>0.01558065647748845</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04187499208290379</v>
+        <v>0.04187499208290339</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05412458335326349</v>
+        <v>0.05412458335326303</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03255732637029948</v>
+        <v>0.03255732637029933</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04254122616736943</v>
+        <v>0.04254122616736909</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0376184834426445</v>
+        <v>0.0376184834426441</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04702605625434901</v>
+        <v>0.04702605625434977</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01387067931008717</v>
+        <v>0.01387067931008678</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1185507360201306</v>
+        <v>0.1185507360201303</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05816170088682049</v>
+        <v>0.0581617008868201</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1032352469333985</v>
+        <v>0.1032352469333979</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04447315477027959</v>
+        <v>0.04447315477027917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03547056747259163</v>
+        <v>0.03547056747259118</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08470663568765378</v>
+        <v>0.08470663568765334</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02030700751107899</v>
+        <v>0.02030700751107862</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01922386513776726</v>
+        <v>0.01922386513776724</v>
       </c>
       <c r="W2" t="n">
-        <v>0.07694935175343119</v>
+        <v>0.07694935175343072</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01642636459025336</v>
+        <v>0.01642636459025314</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02441707055723715</v>
+        <v>0.02441707055723704</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01546664075825956</v>
+        <v>0.01546664075825937</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01842157545645758</v>
+        <v>0.01842157545645713</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00737161955031106</v>
+        <v>0.007371619550311044</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001280665717426127</v>
+        <v>0.001280665717425805</v>
       </c>
       <c r="C3" t="n">
         <v>0.001539073537555747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001347365789062439</v>
+        <v>0.001347365789062438</v>
       </c>
       <c r="F3" t="n">
         <v>0.0015775886340017</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001679651893527959</v>
+        <v>0.001679651893527364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001573112221629733</v>
+        <v>0.00157311222162967</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001625469030649986</v>
+        <v>0.001625469030650701</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001354964517703875</v>
+        <v>0.001354964517703654</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001425360554560966</v>
+        <v>0.001425360554560594</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00140810478494977</v>
+        <v>0.00140810478494921</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00121572227370089</v>
+        <v>0.001215722273700657</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001446324673310942</v>
+        <v>0.001446324673310552</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001420932932350076</v>
+        <v>0.001420932932350056</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001611193264953806</v>
+        <v>0.001611193264953472</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001246009827539195</v>
+        <v>0.001246009827539018</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001933696439910585</v>
+        <v>0.001933696439910298</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001274527204968086</v>
+        <v>0.001274527204967676</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001611128320135034</v>
+        <v>0.001611128320134547</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001866754418601175</v>
+        <v>0.001866754418601174</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02860021321862762</v>
+        <v>0.02860021321862729</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02873477185780859</v>
+        <v>0.02873477185780852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03270151941347231</v>
+        <v>0.03270151941347195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03361696768148788</v>
+        <v>0.03361696768148783</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06465000525460646</v>
+        <v>0.06465000525460644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03178739692066562</v>
+        <v>0.03178739692066528</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04137137348516195</v>
+        <v>0.04137137348516157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04583620566124505</v>
+        <v>0.04583620566124466</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04129680248033443</v>
+        <v>0.04129680248033425</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04161420798563408</v>
+        <v>0.04161420798563364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03981992606823521</v>
+        <v>0.03981992606823499</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04325798957873301</v>
+        <v>0.04325798957873361</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0311641303227134</v>
+        <v>0.03116413032271306</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06931878177823791</v>
+        <v>0.06931878177823751</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04730768759599904</v>
+        <v>0.04730768759599869</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06373646584967675</v>
+        <v>0.0637364658496764</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04231837327554373</v>
+        <v>0.04231837327554337</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0390370359192539</v>
+        <v>0.03903703591925344</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05698300462454093</v>
+        <v>0.05698300462454057</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03351009637279335</v>
+        <v>0.03351009637279301</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05537641769988734</v>
+        <v>0.0553764176998874</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05415556572114373</v>
+        <v>0.05415556572114338</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03209564759696221</v>
+        <v>0.03209564759696198</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03500816609032092</v>
+        <v>0.03500816609032077</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03174583952984682</v>
+        <v>0.03174583952984643</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03282287852874483</v>
+        <v>0.03282287852874447</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02873837674573132</v>
+        <v>0.02873837674573127</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02657521820759219</v>
+        <v>0.02657521820759181</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02662361316321264</v>
+        <v>0.02662361316321253</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02654373107000829</v>
+        <v>0.02654373107000821</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02683942357439018</v>
+        <v>0.02683942357439013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02672064398364915</v>
+        <v>0.02672064398364863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03000342025815608</v>
+        <v>0.03000342025815589</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02671000865630602</v>
+        <v>0.02671000865630662</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02660229924783309</v>
+        <v>0.02660229924783254</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02662795777663527</v>
+        <v>0.02662795777663489</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02662166825123926</v>
+        <v>0.02662166825123901</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02655154708495893</v>
+        <v>0.02655154708495841</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02663559895174668</v>
+        <v>0.02663559895174614</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04888745796359733</v>
+        <v>0.04888745796359743</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02669569161741564</v>
+        <v>0.02669569161741526</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02656258654267831</v>
+        <v>0.02656258654267808</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02681324023766391</v>
+        <v>0.02681324023766352</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0265729807918834</v>
+        <v>0.02657298079188287</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02669566794579174</v>
+        <v>0.02669566794579136</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02673191804661301</v>
+        <v>0.02673191804661297</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003006371175569995</v>
+        <v>0.003006371175569549</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003140929814750792</v>
+        <v>0.003140929814750806</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007107677370414658</v>
+        <v>0.007107677370414233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008023125638430089</v>
+        <v>0.008023125638430099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03905616321154872</v>
+        <v>0.03905616321154873</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006162317696364419</v>
+        <v>0.006162317696363947</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01577753144210427</v>
+        <v>0.01577753144210383</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0202423636181874</v>
+        <v>0.02024236361818695</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01232721302304998</v>
+        <v>0.01232721302304984</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01602036594257636</v>
+        <v>0.01602036594257594</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01422608402517768</v>
+        <v>0.01422608402517727</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01766414753567524</v>
+        <v>0.01766414753567529</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005570288279655783</v>
+        <v>0.00557028827965534</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04369370255393666</v>
+        <v>0.04369370255393618</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02168260837169779</v>
+        <v>0.02168260837169734</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03814262380661913</v>
+        <v>0.03814262380661868</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01672453123248611</v>
+        <v>0.01672453123248568</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01344319387619624</v>
+        <v>0.0134431938761957</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0313891625814833</v>
+        <v>0.03138916258148284</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007885017148492079</v>
+        <v>0.007885017148491666</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00743115816182013</v>
+        <v>0.007431158161820117</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02853048649684247</v>
+        <v>0.02853048649684203</v>
       </c>
       <c r="X6" t="n">
-        <v>0.006470568372660685</v>
+        <v>0.006470568372660629</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009414324047263322</v>
+        <v>0.009414324047263056</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.006151997486789304</v>
+        <v>0.006151997486788732</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007229036485687193</v>
+        <v>0.007229036485686741</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003144534702673531</v>
+        <v>0.003144534702673527</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000981376164534115</v>
+        <v>0.0009813761645341048</v>
       </c>
       <c r="C7" t="n">
         <v>0.001029771120154843</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009498890269504867</v>
+        <v>0.0009498890269504856</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001245581531332418</v>
+        <v>0.001245581531332417</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001095564759347523</v>
+        <v>0.001095564759347283</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001033830800871611</v>
+        <v>0.001033830800871536</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001116166613248237</v>
+        <v>0.001116166613248262</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001008457204775028</v>
+        <v>0.001008457204774819</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001002878552333963</v>
+        <v>0.001002878552333556</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009965890269380557</v>
+        <v>0.0009965890269376843</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009577050419010097</v>
+        <v>0.0009577050419007073</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001010519727445412</v>
+        <v>0.001010519727444805</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009421984255301139</v>
+        <v>0.0009421984255301246</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00107061239311426</v>
+        <v>0.001070612393113902</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009375073183771886</v>
+        <v>0.0009375073183767582</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001219398194606198</v>
+        <v>0.001219398194605805</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009791387488256192</v>
+        <v>0.0009791387488251699</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001101825902734148</v>
+        <v>0.001101825902733644</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001138076003555261</v>
+        <v>0.00113807600355526</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00382083547976183</v>
+        <v>0.003820835479761833</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009816350911196219</v>
+        <v>0.009816350911196208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009712363816031909</v>
+        <v>0.009712363816031929</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1260021171118622</v>
+        <v>0.1260021171118623</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0298873569354941</v>
+        <v>0.02988735693549413</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04975452430425303</v>
+        <v>0.04975452430425304</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02165392660209205</v>
+        <v>0.02165392660209203</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01450250656991646</v>
+        <v>0.01450250656991647</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07670809636988456</v>
+        <v>0.07670809636988461</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01726502754075825</v>
+        <v>0.01726502754075829</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00593019191804922</v>
+        <v>0.005930191918049221</v>
       </c>
       <c r="M2" t="n">
         <v>0.1036038230627586</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07191654549259396</v>
+        <v>0.07191654549259399</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2556754972536334</v>
+        <v>0.2556754972536335</v>
       </c>
       <c r="P2" t="n">
         <v>0.168705203344454</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.09922002948454155</v>
+        <v>0.09922002948454153</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01691533327118754</v>
+        <v>0.01691533327118753</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007346196392928326</v>
+        <v>0.00734619639292834</v>
       </c>
       <c r="T2" t="n">
         <v>0.1089038439441318</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07834470728088508</v>
+        <v>0.07834470728088526</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08837025124488615</v>
+        <v>0.08837025124488622</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1806609286426809</v>
+        <v>0.1806609286426812</v>
       </c>
       <c r="X2" t="n">
-        <v>0.006221751619833468</v>
+        <v>0.006221751619833488</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1568916512766164</v>
+        <v>0.1568916512766165</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.09582390128490967</v>
+        <v>0.09582390128490979</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01858704987804924</v>
+        <v>0.01858704987804922</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.07417129868737786</v>
+        <v>0.07417129868737793</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002546693472019553</v>
+        <v>0.002546693472019583</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002913336418190942</v>
+        <v>0.002913336418190941</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002741096508703248</v>
+        <v>0.002741096508703249</v>
       </c>
       <c r="F3" t="n">
         <v>0.002427878195606609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00328510813411517</v>
+        <v>0.003285108134115228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003081886353525996</v>
+        <v>0.003081886353526006</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00313843516568485</v>
+        <v>0.003138435165684851</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002684200300116589</v>
+        <v>0.002684200300116599</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002814484176939976</v>
+        <v>0.002814484176940004</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002782548450670279</v>
+        <v>0.002782548450670309</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0024265008589465</v>
+        <v>0.002426500858946513</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002859184341498121</v>
+        <v>0.002859184341498102</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002809977884938758</v>
+        <v>0.002809977884938718</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003158409872369708</v>
+        <v>0.003158409872369745</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002482554865945157</v>
+        <v>0.002482554865945167</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003765370744317933</v>
+        <v>0.003765370744317925</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002535332758578748</v>
+        <v>0.002535332758578738</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00315828967690785</v>
+        <v>0.003158289676907882</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003740171203912675</v>
+        <v>0.003740171203912672</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03114707338173693</v>
+        <v>0.03114707338173696</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03317669768129711</v>
+        <v>0.03317669768129714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03329446627848886</v>
+        <v>0.03329446627848887</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07562254346242507</v>
+        <v>0.07562254346242511</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04051195459346078</v>
+        <v>0.04051195459346081</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04788936357765764</v>
+        <v>0.04788936357765761</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03764702568909781</v>
+        <v>0.03764702568909793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03504041706358365</v>
+        <v>0.03504041706358377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06137070176940222</v>
+        <v>0.06137070176940227</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03604732351829646</v>
+        <v>0.0360473235182965</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03191590903417885</v>
+        <v>0.03191590903417887</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06750418286971588</v>
+        <v>0.06750418286971591</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05596716006121617</v>
+        <v>0.05596716006121622</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1229451401715604</v>
+        <v>0.1229451401715605</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09124548929841665</v>
+        <v>0.09124548929841678</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06591895936258492</v>
+        <v>0.06591895936258493</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03591986406335537</v>
+        <v>0.03591986406335539</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03243202603770825</v>
+        <v>0.03243202603770828</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06944859602001516</v>
+        <v>0.06944859602001514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05831014954976159</v>
+        <v>0.05831014954976162</v>
       </c>
       <c r="V4" t="n">
         <v>0.08657268476067564</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0956032107784059</v>
+        <v>0.095603210778406</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03202217912181233</v>
+        <v>0.03202217912181236</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08693958829142204</v>
+        <v>0.08693958829142209</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06468111051316991</v>
+        <v>0.06468111051316992</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03652918513626898</v>
+        <v>0.03652918513626897</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05675277848979644</v>
+        <v>0.05675277848979648</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0306826635816457</v>
+        <v>0.03068266358164581</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03066062995788536</v>
+        <v>0.03066062995788542</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03069534885655393</v>
+        <v>0.03069534885655395</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03050329703825074</v>
+        <v>0.03050329703825078</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03095180705507683</v>
+        <v>0.03095180705507693</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03453481278104747</v>
+        <v>0.0345348127810475</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03088572870537898</v>
+        <v>0.03088572870537899</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03073278320580039</v>
+        <v>0.03073278320580042</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03078027014903198</v>
+        <v>0.03078027014903207</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03076862995181493</v>
+        <v>0.03076862995181496</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0306388547855535</v>
+        <v>0.03063885478555355</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03079656283411761</v>
+        <v>0.0307965628341176</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05538696982042977</v>
+        <v>0.05538696982042976</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03090562702643672</v>
+        <v>0.03090562702643673</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03065928581288515</v>
+        <v>0.03065928581288517</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03112685713696746</v>
+        <v>0.03112685713696752</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03067852273500077</v>
+        <v>0.03067852273500083</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03090558321660226</v>
+        <v>0.0309055832166023</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03108145956612798</v>
+        <v>0.03108145956612801</v>
       </c>
     </row>
     <row r="6">
@@ -4358,37 +4358,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002441108233603768</v>
+        <v>0.002441108233603758</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004470732533163931</v>
+        <v>0.004470732533163935</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004588501130355657</v>
+        <v>0.004588501130355645</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04691657831429194</v>
+        <v>0.04691657831429192</v>
       </c>
       <c r="F6" t="n">
         <v>0.01180598944532761</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01914167857328248</v>
+        <v>0.01914167857328242</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008941060540964677</v>
+        <v>0.008941060540964735</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006334451915450471</v>
+        <v>0.006334451915450528</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02891914688834651</v>
+        <v>0.02891914688834656</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007341358370163274</v>
+        <v>0.007341358370163282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003209943886045675</v>
+        <v>0.003209943886045664</v>
       </c>
       <c r="M6" t="n">
         <v>0.03879821772158269</v>
@@ -4397,46 +4397,46 @@
         <v>0.02726119491308299</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09419745516718525</v>
+        <v>0.09419745516718529</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06249780429404156</v>
+        <v>0.06249780429404159</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03721299421445175</v>
+        <v>0.03721299421445173</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007213898915222186</v>
+        <v>0.007213898915222177</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003726060889575073</v>
+        <v>0.003726060889575069</v>
       </c>
       <c r="T6" t="n">
         <v>0.04074263087188187</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02956246454538647</v>
+        <v>0.0295624645453865</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03310475406611563</v>
+        <v>0.03310475406611567</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06685552577403077</v>
+        <v>0.0668555257740308</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003274494117437167</v>
+        <v>0.003274494117437164</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.05823362314328891</v>
+        <v>0.05823362314328889</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03597514536503667</v>
+        <v>0.03597514536503671</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007823219988135791</v>
+        <v>0.007823219988135777</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02804681334166329</v>
+        <v>0.02804681334166328</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001976698433512559</v>
+        <v>0.001976698433512608</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0019546648097522</v>
+        <v>0.001954664809752202</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001989383708420742</v>
+        <v>0.001989383708420741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001797331890117555</v>
+        <v>0.001797331890117557</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00220412205070167</v>
+        <v>0.002204122050701726</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002083257899991751</v>
+        <v>0.002083257899991747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002179763557245761</v>
+        <v>0.002179763557245762</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002026818057667222</v>
+        <v>0.002026818057667205</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002032585144656824</v>
+        <v>0.002032585144656868</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002020944947439753</v>
+        <v>0.002020944947439758</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001932889637420336</v>
+        <v>0.001932889637420348</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002048877829742436</v>
+        <v>0.002048877829742416</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001919039125869725</v>
+        <v>0.001919039125869724</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002157942022061557</v>
+        <v>0.002157942022061553</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001911600808509982</v>
+        <v>0.001911600808509955</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002420891988834272</v>
+        <v>0.002420891988834317</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001972557586867599</v>
+        <v>0.00197255758686762</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00219961806846911</v>
+        <v>0.002199618068469111</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002375494417994796</v>
+        <v>0.002375494417994799</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002523981836344913</v>
+        <v>0.002523981836344834</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009666396125131375</v>
+        <v>0.009666396125131345</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004382211030550003</v>
+        <v>0.004382211030549926</v>
       </c>
       <c r="E2" t="n">
         <v>0.0426513640750442</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07110401502277085</v>
+        <v>0.0711040150227709</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04802848421049349</v>
+        <v>0.04802848421049334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01455983024551163</v>
+        <v>0.01455983024551156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009790257268806151</v>
+        <v>0.00979025726880607</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05743829289195383</v>
+        <v>0.05743829289195375</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006844033815386584</v>
+        <v>0.006844033815386493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003989051298199705</v>
+        <v>0.003989051298199623</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08666651243595064</v>
+        <v>0.08666651243595055</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05891378063440381</v>
+        <v>0.0589137806344037</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2590161985871802</v>
+        <v>0.2590161985871798</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1641732618746858</v>
+        <v>0.1641732618746855</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05237445547794931</v>
+        <v>0.05237445547794917</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005693039844583188</v>
+        <v>0.005693039844583083</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007264187638994148</v>
+        <v>0.007264187638994064</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08251150707921516</v>
+        <v>0.08251150707921515</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07259327575468887</v>
+        <v>0.07259327575468878</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06087485729682142</v>
+        <v>0.06087485729682132</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1117145871840826</v>
+        <v>0.1117145871840823</v>
       </c>
       <c r="X2" t="n">
-        <v>0.07879806935181903</v>
+        <v>0.07879806935181898</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1141242153336429</v>
+        <v>0.1141242153336427</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03416091231956751</v>
+        <v>0.03416091231956736</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01502580918542745</v>
+        <v>0.01502580918542738</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08132049519846957</v>
+        <v>0.08132049519846959</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001904138278607859</v>
+        <v>0.001904138278607887</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002276736839310676</v>
+        <v>0.002276736839310651</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002030848164618395</v>
+        <v>0.002030848164618386</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002057242655509942</v>
+        <v>0.002057242655509937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002479532976214851</v>
+        <v>0.002479532976214875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002354228453335405</v>
+        <v>0.002354228453335339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002461296928480062</v>
+        <v>0.002461296928480053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002011287694562021</v>
+        <v>0.002011287694562011</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002112808771758391</v>
+        <v>0.002112808771758263</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002087923502674195</v>
+        <v>0.002087923502674212</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001810480614688456</v>
+        <v>0.001810480614688487</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002146763361245673</v>
+        <v>0.002146763361245646</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002174391085309444</v>
+        <v>0.002174391085309338</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002380805917104344</v>
+        <v>0.002380805917104257</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001854159566461728</v>
+        <v>0.001854159566461653</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002852267426045182</v>
+        <v>0.002852267426045108</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001895285672327282</v>
+        <v>0.001895285672327236</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002380712257203396</v>
+        <v>0.002380712257203259</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00299799871442314</v>
+        <v>0.00299799871442313</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.029037542199584</v>
+        <v>0.0290375421995839</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03157479073837181</v>
+        <v>0.03157479073837178</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02971484492044289</v>
+        <v>0.0297148449204428</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04360242755429513</v>
+        <v>0.04360242755429511</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05408427526730215</v>
+        <v>0.05408427526730217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04562339897411649</v>
+        <v>0.04562339897411643</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03342446761265772</v>
+        <v>0.03342446761265758</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03168601426980212</v>
+        <v>0.03168601426980202</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05260628088945351</v>
+        <v>0.05260628088945347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03061215041733317</v>
+        <v>0.03061215041733307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02957154281471587</v>
+        <v>0.02957154281471575</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05975771905653064</v>
+        <v>0.05975771905653059</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04959096169902785</v>
+        <v>0.04959096169902768</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1225259433215908</v>
+        <v>0.1225259433215906</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08795680659187795</v>
+        <v>0.08795680659187775</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04720745446813304</v>
+        <v>0.04720745446813308</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03019262663062891</v>
+        <v>0.0301926266306288</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03076529155234283</v>
+        <v>0.03076529155234272</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05819205588966756</v>
+        <v>0.05819205588966751</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05457697703763002</v>
+        <v>0.0545769770376299</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07407614421193356</v>
+        <v>0.07407614421193343</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06883623566801184</v>
+        <v>0.0688362356680117</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05683855144341897</v>
+        <v>0.05683855144341886</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06971451683324423</v>
+        <v>0.06971451683324413</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0405688318611247</v>
+        <v>0.04056883186112458</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03359431146445602</v>
+        <v>0.03359431146445592</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05783386751007286</v>
+        <v>0.05783386751007283</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02881161650135938</v>
+        <v>0.02881161650135909</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02888134670245055</v>
+        <v>0.02888134670245042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02879672649512493</v>
+        <v>0.02879672649512492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02891753752757166</v>
+        <v>0.02891753752757162</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02902134111201145</v>
+        <v>0.02902134111201141</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03252878623131879</v>
+        <v>0.03252878623131875</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02906590679161986</v>
+        <v>0.02906590679161983</v>
       </c>
       <c r="N5" t="n">
         <v>0.02885067120526267</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02888767444578005</v>
+        <v>0.02888767444578009</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02887860405741648</v>
+        <v>0.02887860405741645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02877747938264456</v>
+        <v>0.02877747938264449</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02890005049493328</v>
+        <v>0.02890005049493326</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0526805135735127</v>
+        <v>0.05268051357351262</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02898535625827733</v>
+        <v>0.02898535625827727</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02879339984766183</v>
+        <v>0.02879339984766166</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02915719844210569</v>
+        <v>0.02915719844210557</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02880838983032266</v>
+        <v>0.02880838983032262</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02898532212034324</v>
+        <v>0.02898532212034311</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02928623725082582</v>
+        <v>0.02928623725082579</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001688824963747647</v>
+        <v>0.001688824963747575</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004226073502535506</v>
+        <v>0.004226073502535467</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002366127684606537</v>
+        <v>0.002366127684606465</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01625371031845878</v>
+        <v>0.01625371031845877</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02673555803146582</v>
+        <v>0.02673555803146586</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01823925428609322</v>
+        <v>0.01823925428609312</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006075750376821339</v>
+        <v>0.006075750376821273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004337297033965765</v>
+        <v>0.0043372970339657</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02165369043262097</v>
+        <v>0.02165369043262089</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00326343318149682</v>
+        <v>0.003263433181496743</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002222825578879518</v>
+        <v>0.002222825578879447</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0324090018206943</v>
+        <v>0.03240900182069426</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02224224446319143</v>
+        <v>0.02224224446319136</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09514179863356738</v>
+        <v>0.09514179863356731</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06057266190385455</v>
+        <v>0.06057266190385448</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01985873723229666</v>
+        <v>0.01985873723229671</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002843909394792559</v>
+        <v>0.002843909394792485</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003416574316506474</v>
+        <v>0.003416574316506415</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03084333865383122</v>
+        <v>0.03084333865383118</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02719283234960668</v>
+        <v>0.02719283234960659</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02287659939461001</v>
+        <v>0.02287659939461005</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04145209097998848</v>
+        <v>0.04145209097998834</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02945440675539564</v>
+        <v>0.02945440675539555</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04236579959740797</v>
+        <v>0.04236579959740782</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01322011462528835</v>
+        <v>0.01322011462528824</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.006245594228619693</v>
+        <v>0.006245594228619621</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03048515027423655</v>
+        <v>0.03048515027423653</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001462899265523013</v>
+        <v>0.001462899265522778</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00153262946661421</v>
+        <v>0.001532629466614139</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001448009259288595</v>
+        <v>0.001448009259288589</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001568820291735311</v>
+        <v>0.001568820291735305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001637196423988131</v>
+        <v>0.001637196423988075</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001576195774486224</v>
+        <v>0.001576195774486122</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001717189555783521</v>
+        <v>0.001717189555783514</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001501953969426371</v>
+        <v>0.001501953969426329</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001503529757756771</v>
+        <v>0.001503529757756759</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001494459369393152</v>
+        <v>0.001494459369393145</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001428762146808177</v>
+        <v>0.001428762146808181</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001515905806909938</v>
+        <v>0.001515905806909937</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001480968756189253</v>
+        <v>0.001480968756189213</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00160121157025401</v>
+        <v>0.00160121157025398</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001409255159638412</v>
+        <v>0.00140925515963835</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001808481206269347</v>
+        <v>0.001808481206269242</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001459672594486347</v>
+        <v>0.001459672594486275</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001636604884506861</v>
+        <v>0.001636604884506797</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001937520014989464</v>
+        <v>0.001937520014989457</v>
       </c>
     </row>
   </sheetData>
@@ -5374,43 +5374,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0022085907055686</v>
+        <v>0.002208590705568564</v>
       </c>
       <c r="C2" t="n">
         <v>0.006420785931193392</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007875721748242668</v>
+        <v>0.0078757217482426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004945411300903231</v>
+        <v>0.004945411300903233</v>
       </c>
       <c r="F2" t="n">
         <v>0.1062312246651275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02273806392620812</v>
+        <v>0.02273806392620809</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02356597716614265</v>
+        <v>0.0235659771661427</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01545327051189611</v>
+        <v>0.01545327051189607</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03972959884913446</v>
+        <v>0.03972959884913453</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0200961136726395</v>
+        <v>0.02009611367263943</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01290116818845607</v>
+        <v>0.01290116818845604</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07427677914997598</v>
+        <v>0.07427677914997627</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03209294574483961</v>
+        <v>0.03209294574483959</v>
       </c>
       <c r="O2" t="n">
         <v>0.1933939930220587</v>
@@ -5419,40 +5419,40 @@
         <v>0.1480158023052901</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02420977742632467</v>
+        <v>0.02420977742632464</v>
       </c>
       <c r="R2" t="n">
-        <v>0.008381809757266639</v>
+        <v>0.008381809757266602</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05466624362614368</v>
+        <v>0.05466624362614354</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06913252844355572</v>
+        <v>0.06913252844355569</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06497309384712925</v>
+        <v>0.06497309384712915</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03037952345453293</v>
+        <v>0.03037952345453296</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04062486909544456</v>
+        <v>0.04062486909544453</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08313699279049042</v>
+        <v>0.08313699279049037</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07824679017117954</v>
+        <v>0.07824679017117948</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008664392393282724</v>
+        <v>0.008664392393282639</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02056199555089018</v>
+        <v>0.02056199555089022</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0626827741950107</v>
+        <v>0.06268277419501063</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001326500554607071</v>
+        <v>0.001326500554607066</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001628786181444927</v>
+        <v>0.001628786181444926</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001398367307744289</v>
+        <v>0.001398367307744286</v>
       </c>
       <c r="F3" t="n">
         <v>0.001654874229178605</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001750378966677262</v>
+        <v>0.001750378966677214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00166337149300569</v>
+        <v>0.001663371493005723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001793003947481346</v>
+        <v>0.001793003947481634</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001405434761811109</v>
+        <v>0.001405434761811035</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001480222717220938</v>
+        <v>0.001480222717220788</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001461890382243036</v>
+        <v>0.001461890382242989</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001257505372652481</v>
+        <v>0.001257505372652413</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001504113688005325</v>
+        <v>0.001504113688005337</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001528393665904861</v>
+        <v>0.001528393665904859</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001677649292191644</v>
+        <v>0.001677649292191505</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001289682528241146</v>
+        <v>0.001289682528241134</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002023042540652833</v>
+        <v>0.00202304254065276</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001319979068212161</v>
+        <v>0.001319979068212159</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001677580295387012</v>
+        <v>0.001677580295386963</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002173287483051579</v>
+        <v>0.002173287483051588</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02708481386652032</v>
+        <v>0.02708481386652026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0285891003317874</v>
+        <v>0.02858910033178736</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02915041658476253</v>
+        <v>0.0291504165847624</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02802371201838169</v>
+        <v>0.02802371201838168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06517376901971939</v>
+        <v>0.06517376901971934</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03456756578619783</v>
+        <v>0.03456756578619777</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03486933044030589</v>
+        <v>0.0348693304403058</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0319123441290442</v>
+        <v>0.03191234412904413</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04419532945385281</v>
+        <v>0.04419532945385277</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03360460594211822</v>
+        <v>0.03360460594211811</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03098213280044883</v>
+        <v>0.03098213280044876</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05342617537339072</v>
+        <v>0.05342617537339094</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03797731035852054</v>
+        <v>0.03797731035852047</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09676964799854124</v>
+        <v>0.0967696479985411</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08022983033989722</v>
+        <v>0.08022983033989714</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03510398807525787</v>
+        <v>0.03510398807525777</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02933487972126632</v>
+        <v>0.02933487972126623</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04620501236720936</v>
+        <v>0.04620501236720923</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0514778033114633</v>
+        <v>0.05147780331146325</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04996173824361284</v>
+        <v>0.04996173824361273</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06029512812152316</v>
+        <v>0.06029512812152328</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04108709623291382</v>
+        <v>0.0410870962329138</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05658226611719805</v>
+        <v>0.0565822661171979</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05479984468611747</v>
+        <v>0.05479984468611742</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02943787777384131</v>
+        <v>0.02943787777384124</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03377441441607938</v>
+        <v>0.03377441441607933</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.04920890877839832</v>
+        <v>0.04920890877839822</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02676330236452039</v>
+        <v>0.02676330236452032</v>
       </c>
       <c r="C5" t="n">
         <v>0.02684247269350611</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02673085613436873</v>
+        <v>0.0267308561343687</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02705691728332179</v>
+        <v>0.02705691728332178</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0269178010682883</v>
+        <v>0.02691780106828828</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03032063657875337</v>
+        <v>0.03032063657875333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02700669045954247</v>
+        <v>0.0270066904595427</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0267920729561539</v>
+        <v>0.02679207295615384</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02681933228769623</v>
+        <v>0.02681933228769625</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0268126503668661</v>
+        <v>0.026812650366866</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02673815443088025</v>
+        <v>0.02673815443088014</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02682804026600529</v>
+        <v>0.02682804026600522</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04977923010063882</v>
+        <v>0.04977923010063889</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0268912919559732</v>
+        <v>0.02689129195597317</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02674988262624911</v>
+        <v>0.02674988262624899</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02701718373922506</v>
+        <v>0.02701718373922501</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02676092535930857</v>
+        <v>0.02676092535930853</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02689126680744812</v>
+        <v>0.02689126680744813</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02715391141015571</v>
+        <v>0.02715391141015567</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001327667959794203</v>
+        <v>0.001327667959794048</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002831954425061155</v>
+        <v>0.002831954425061154</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003393270678036387</v>
+        <v>0.003393270678036219</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002266566111655471</v>
+        <v>0.002266566111655469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03941662311299313</v>
+        <v>0.03941662311299316</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008779616102963675</v>
+        <v>0.008779616102963681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009112184533579735</v>
+        <v>0.009112184533579603</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006155198222318068</v>
+        <v>0.006155198222317922</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01496507657532818</v>
+        <v>0.01496507657532816</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007847460035392101</v>
+        <v>0.0078474600353919</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005224986893722702</v>
+        <v>0.00522498689372255</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02766902946666451</v>
+        <v>0.02766902946666476</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01222016445179441</v>
+        <v>0.01222016445179427</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0709816983153071</v>
+        <v>0.070981698315307</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05444188065666312</v>
+        <v>0.05444188065666306</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009346842168531724</v>
+        <v>0.009346842168531572</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003577733814540188</v>
+        <v>0.003577733814540036</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02044786646048324</v>
+        <v>0.02044786646048306</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02572065740473718</v>
+        <v>0.02572065740473702</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02417378856037871</v>
+        <v>0.02417378856037861</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01153449326807658</v>
+        <v>0.01153449326807659</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01529914654967974</v>
+        <v>0.01529914654967968</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03079431643396391</v>
+        <v>0.0307943164339638</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02904269877939139</v>
+        <v>0.02904269877939125</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003680731867115162</v>
+        <v>0.003680731867115039</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008017268509353272</v>
+        <v>0.008017268509353109</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02345176287167209</v>
+        <v>0.02345176287167203</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001006156457794135</v>
+        <v>0.001006156457794112</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001085326786779878</v>
+        <v>0.001085326786779876</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000973710227642499</v>
+        <v>0.0009737102276424973</v>
       </c>
       <c r="F7" t="n">
         <v>0.001299771376595565</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001129851385054179</v>
+        <v>0.001129851385054207</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001090383700228714</v>
+        <v>0.00109038370022871</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001249544552816239</v>
+        <v>0.001249544552816484</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001034927049427761</v>
+        <v>0.001034927049427651</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001031382604462151</v>
+        <v>0.001031382604462167</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001024700683631996</v>
+        <v>0.001024700683631902</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009810085241539761</v>
+        <v>0.0009810085241539509</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001040090582771178</v>
+        <v>0.001040090582771138</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00101859524719226</v>
+        <v>0.001018595247192258</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001103342272739076</v>
+        <v>0.001103342272739082</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009619329430149992</v>
+        <v>0.0009619329430148863</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001260037832498926</v>
+        <v>0.001260037832498799</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001003779452582306</v>
+        <v>0.001003779452582318</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001134120900721913</v>
+        <v>0.001134120900721912</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001396765503429508</v>
+        <v>0.001396765503429489</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003351686918307913</v>
+        <v>0.003351686918308378</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01024245969913981</v>
+        <v>0.01024245969914028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007825375505450774</v>
+        <v>0.007825375505451293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1204814044637621</v>
+        <v>0.1204814044637625</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02635823899369072</v>
+        <v>0.02635823899369071</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0210048340001899</v>
+        <v>0.02100483400019047</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04097700014707528</v>
+        <v>0.04097700014707581</v>
       </c>
       <c r="I2" t="n">
-        <v>0.019357759339871</v>
+        <v>0.01935775933987144</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05086235500987676</v>
+        <v>0.0508623550098769</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02429457109688114</v>
+        <v>0.02429457109688159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004057708473515462</v>
+        <v>0.004057708473515912</v>
       </c>
       <c r="M2" t="n">
         <v>0.03536673891806458</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03028168838651619</v>
+        <v>0.03028168838651664</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1411639624625588</v>
+        <v>0.141163962462559</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1013411507282024</v>
+        <v>0.1013411507282027</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03606068398155822</v>
+        <v>0.03606068398155868</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02741774675170227</v>
+        <v>0.02741774675170202</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004447556256378588</v>
+        <v>0.004447556256379041</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06428296720540687</v>
+        <v>0.06428296720540733</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05882384124002816</v>
+        <v>0.05882384124002878</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08484894740887375</v>
+        <v>0.08484894740887371</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1641665657973127</v>
+        <v>0.1641665657973132</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00645783577764894</v>
+        <v>0.006457835777649416</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.134383563107484</v>
+        <v>0.1343835631074845</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08719415919350254</v>
+        <v>0.08719415919350293</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01815162246289073</v>
+        <v>0.01815162246289116</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01773795615551737</v>
+        <v>0.0177379561555174</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002100718599784369</v>
+        <v>0.002100718599784909</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002394654581316168</v>
+        <v>0.00239465458131623</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002282002623129881</v>
+        <v>0.002282002623130165</v>
       </c>
       <c r="F3" t="n">
         <v>0.002002515433075763</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002699238871942146</v>
+        <v>0.002699238871942254</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002532815679782614</v>
+        <v>0.002532815679782665</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="M3" t="n">
         <v>0.00243326310256864</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002212174436688983</v>
+        <v>0.002212174436689286</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002317775727350456</v>
+        <v>0.002317775727350677</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002291890299365441</v>
+        <v>0.002291890299365945</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002003296759253914</v>
+        <v>0.002003296759253955</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002355529526423246</v>
+        <v>0.002355529526423308</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002330144277785361</v>
+        <v>0.002330144277785458</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002596543892943448</v>
+        <v>0.002596543892944036</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00204873120303154</v>
+        <v>0.002048731203032144</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003091118620567433</v>
+        <v>0.003091118620567673</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002091510200169597</v>
+        <v>0.002091510200169628</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002596446468960023</v>
+        <v>0.002596446468960488</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002912202214634497</v>
+        <v>0.002912202214634499</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0292015530726315</v>
+        <v>0.02920155307263222</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03158491772154778</v>
+        <v>0.03158491772154833</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03083216002994136</v>
+        <v>0.03083216002994227</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07186187693139483</v>
+        <v>0.07186187693139524</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03747568219453387</v>
+        <v>0.03747568219453403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03563591789025874</v>
+        <v>0.03563591789025932</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04291553792578281</v>
+        <v>0.04291553792578345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03503557851749953</v>
+        <v>0.03503557851750037</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05035975733677182</v>
+        <v>0.0503597573367719</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03683498843195923</v>
+        <v>0.03683498843195989</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02945888963898095</v>
+        <v>0.02945888963898159</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04076695864128428</v>
+        <v>0.0407669586412846</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03901722237975053</v>
+        <v>0.03901722237975117</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07943250923506834</v>
+        <v>0.07943250923506885</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06491756198096019</v>
+        <v>0.06491756198096062</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04112359841375098</v>
+        <v>0.04112359841375166</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03797334928396141</v>
+        <v>0.03797334928396205</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02960098457801082</v>
+        <v>0.02960098457801146</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05141028924606233</v>
+        <v>0.05141028924606306</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04942050193597531</v>
+        <v>0.04942050193597609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08471928905910751</v>
+        <v>0.08471928905910743</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08781668804038063</v>
+        <v>0.08781668804038149</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03033370785761993</v>
+        <v>0.03033370785762061</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07696113328961261</v>
+        <v>0.07696113328961347</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05976114968892377</v>
+        <v>0.05976114968892451</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03459595578901453</v>
+        <v>0.03459595578901531</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03431675921756875</v>
+        <v>0.03431675921756896</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02874558981014128</v>
+        <v>0.02874558981014219</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02872448490968146</v>
+        <v>0.02872448490968179</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02877958292793629</v>
+        <v>0.02877958292793689</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02859830695603525</v>
+        <v>0.02859830695603536</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02896374342116296</v>
+        <v>0.02896374342116364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03274420776505591</v>
+        <v>0.03274420776505654</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02876309343093392</v>
+        <v>0.02876309343093408</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02878621415391254</v>
+        <v>0.02878621415391301</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02882470458432572</v>
+        <v>0.02882470458432578</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02881526964978719</v>
+        <v>0.02881526964978759</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02871008069325297</v>
+        <v>0.02871008069325363</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02883846540076025</v>
+        <v>0.02883846540076096</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05464215430253409</v>
+        <v>0.05464215430253422</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02892631230722326</v>
+        <v>0.02892631230722391</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02872664101449179</v>
+        <v>0.0287266410144927</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02910657898785255</v>
+        <v>0.02910657898785269</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02874223345661223</v>
+        <v>0.02874223345661303</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02892627679732532</v>
+        <v>0.02892627679732593</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02891294599890929</v>
+        <v>0.02891294599890953</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002100794871391789</v>
+        <v>0.002100794871392307</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004484159520308293</v>
+        <v>0.00448415952030834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003731401828701678</v>
+        <v>0.003731401828702251</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04476111873015513</v>
+        <v>0.04476111873015532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01037492399329414</v>
+        <v>0.01037492399329413</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008495222606975699</v>
+        <v>0.008495222606976138</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01581477972454308</v>
+        <v>0.0158147797245436</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00793482031625984</v>
+        <v>0.007934820316260336</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01933921147815874</v>
+        <v>0.01933921147815907</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009734230230719553</v>
+        <v>0.009734230230719988</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002358131437741289</v>
+        <v>0.002358131437741763</v>
       </c>
       <c r="M6" t="n">
         <v>0.01366620044004456</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01191646417851081</v>
+        <v>0.01191646417851129</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0522918139517853</v>
+        <v>0.05229181395178566</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0377768666976771</v>
+        <v>0.03777686669767725</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01402284021251123</v>
+        <v>0.01402284021251173</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01087259108272171</v>
+        <v>0.0108725910827222</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0025002263767711</v>
+        <v>0.002500226376771583</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02430953104482263</v>
+        <v>0.02430953104482312</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02227980665269228</v>
+        <v>0.02227980665269273</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03168453430815141</v>
+        <v>0.03168453430815137</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06067599275709751</v>
+        <v>0.06067599275709821</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003193012574336857</v>
+        <v>0.003193012574337381</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04986037508837297</v>
+        <v>0.04986037508837345</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03266039148768408</v>
+        <v>0.03266039148768454</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007495197587774803</v>
+        <v>0.007495197587775304</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007216001016329014</v>
+        <v>0.00721600101632902</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00164483160890156</v>
+        <v>0.00164483160890216</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001623726708441734</v>
+        <v>0.001623726708441801</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001678824726696586</v>
+        <v>0.00167882472669683</v>
       </c>
       <c r="F7" t="n">
         <v>0.001497548754795532</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001823048137879888</v>
+        <v>0.001823048137880434</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00172366190644283</v>
+        <v>0.001723661906443025</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001662335229694209</v>
+        <v>0.00166233522969421</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001685455952672842</v>
+        <v>0.001685455952673131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001684009301042625</v>
+        <v>0.00168400930104261</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00167457436650412</v>
+        <v>0.001674574366504339</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001609322492013257</v>
+        <v>0.001609322492013677</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001697770117477171</v>
+        <v>0.001697770117477571</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001607399551578093</v>
+        <v>0.001607399551578019</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001785617023940229</v>
+        <v>0.001785617023940794</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001585945731208712</v>
+        <v>0.001585945731209349</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002005820786612819</v>
+        <v>0.002005820786612829</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001641475255372495</v>
+        <v>0.00164147525537303</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001825518596085597</v>
+        <v>0.001825518596086081</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001812187797669551</v>
+        <v>0.001812187797669554</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001990117348490105</v>
+        <v>0.001990117348490058</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008411420268153658</v>
+        <v>0.008411420268153646</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00328756407591542</v>
+        <v>0.00328756407591543</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07467336426032679</v>
+        <v>0.07467336426032692</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07952482099769995</v>
+        <v>0.07952482099769989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01908513604082331</v>
+        <v>0.01908513604082415</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0308173272437753</v>
+        <v>0.03081732724377527</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007514218504614371</v>
+        <v>0.007514218504614455</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05591877565131572</v>
+        <v>0.05591877565131533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01364195705580003</v>
+        <v>0.01364195705580001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003597301746322699</v>
+        <v>0.00359730174632268</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1560071836495483</v>
+        <v>0.1560071836495482</v>
       </c>
       <c r="N2" t="n">
         <v>0.03802787054719691</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2293262102810667</v>
+        <v>0.2293262102810666</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1228826036527045</v>
+        <v>0.1228826036527044</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05998206231440914</v>
+        <v>0.05998206231440915</v>
       </c>
       <c r="R2" t="n">
         <v>0.01057879119731824</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005658116622848161</v>
+        <v>0.005658116622848122</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0761353231088116</v>
+        <v>0.07613532310881164</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08416045614652826</v>
+        <v>0.08416045614652833</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05713924767902103</v>
+        <v>0.05713924767902098</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1173214950287059</v>
+        <v>0.117321495028706</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0413427083637538</v>
+        <v>0.04134270836375367</v>
       </c>
       <c r="Y2" t="n">
         <v>0.1023515843898119</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04394470207056919</v>
+        <v>0.04394470207056914</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01504146683789348</v>
+        <v>0.01504146683789287</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04337412729918332</v>
+        <v>0.04337412729918329</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00176034872357428</v>
+        <v>0.001760348723574269</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002095929664983644</v>
+        <v>0.002095929664983621</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001927437479817919</v>
+        <v>0.001927437479817917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001928108049080121</v>
+        <v>0.001928108049080085</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00231570707176749</v>
+        <v>0.002315707071767522</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002194923248660012</v>
+        <v>0.002194923248660031</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002478539152137049</v>
+        <v>0.002478539152137038</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00186376699088296</v>
+        <v>0.001863766990882957</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00196175290899594</v>
+        <v>0.00196175290899592</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001937734192826367</v>
+        <v>0.001937734192826402</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00166995239956101</v>
+        <v>0.001669952399561002</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00199535365200563</v>
+        <v>0.001995353652005636</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002002934600380577</v>
+        <v>0.002002934600380548</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002220417878571605</v>
+        <v>0.002220417878571611</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001712110366232938</v>
+        <v>0.001712110366232935</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00267687954410444</v>
+        <v>0.002676879544104388</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001751804382067303</v>
+        <v>0.001751804382067279</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002220327480153303</v>
+        <v>0.002220327480153268</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002676641153164845</v>
+        <v>0.002676641153164864</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02783384380982135</v>
+        <v>0.02783384380982143</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03009527704899971</v>
+        <v>0.03009527704899944</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02830674790657919</v>
+        <v>0.02830674790657917</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05429555157423876</v>
+        <v>0.05429555157423863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05615540551707209</v>
+        <v>0.05615540551707199</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03406477738333239</v>
+        <v>0.03406477738333148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03834102331046375</v>
+        <v>0.03834102331046361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02984731381395786</v>
+        <v>0.02984731381395767</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05114655354504802</v>
+        <v>0.0511465535450475</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03208080256032608</v>
+        <v>0.03208080256032601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0284196436503193</v>
+        <v>0.02841964365031903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08413535246647356</v>
+        <v>0.08413535246647327</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04096918167408665</v>
+        <v>0.04096918167408656</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1106951801685642</v>
+        <v>0.1106951801685641</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0718977354764611</v>
+        <v>0.07189773547646119</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04897122677410002</v>
+        <v>0.04897122677410007</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03096431457441901</v>
+        <v>0.03096431457441891</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02917078647350277</v>
+        <v>0.02917078647350266</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05485890065249487</v>
+        <v>0.05485890065249474</v>
       </c>
       <c r="U4" t="n">
         <v>0.05778396740887266</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07237906153444928</v>
+        <v>0.07237906153444919</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06987077668484812</v>
+        <v>0.06987077668484819</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04217740113343078</v>
+        <v>0.04217740113343062</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06441442004253697</v>
+        <v>0.06441442004253688</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04312579728541222</v>
+        <v>0.0431257972854121</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03259090744202556</v>
+        <v>0.03259090744202543</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.04290246750980957</v>
+        <v>0.04290246750980966</v>
       </c>
     </row>
     <row r="5">
@@ -7006,82 +7006,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02775009584411896</v>
+        <v>0.02775009584411904</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02779335488437908</v>
+        <v>0.02779335488437894</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02778051548854354</v>
+        <v>0.0277805154885433</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02787231483390751</v>
+        <v>0.02787231483390737</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02795251744068841</v>
+        <v>0.02795251744068834</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03156484020160555</v>
+        <v>0.03156484020160533</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02817596437153154</v>
+        <v>0.02817596437153131</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02778779058815437</v>
+        <v>0.02778779058815415</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02782350530469778</v>
+        <v>0.02782350530469784</v>
       </c>
       <c r="P5" t="n">
-        <v>0.027814750764696</v>
+        <v>0.02781475076469612</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02771714744550333</v>
+        <v>0.02771714744550323</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02783575238096499</v>
+        <v>0.027835752380965</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05228252286056094</v>
+        <v>0.05228252286056089</v>
       </c>
       <c r="W5" t="n">
         <v>0.02791778564871065</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02773251352931142</v>
+        <v>0.02773251352931128</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02808416056575392</v>
+        <v>0.0280841605657539</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02774698153197238</v>
+        <v>0.02774698153197231</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02791775269954875</v>
+        <v>0.02791775269954869</v>
       </c>
       <c r="AB5" t="n">
         <v>0.02806871170359597</v>
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001419373164879136</v>
+        <v>0.001419373164879122</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003680806404057491</v>
+        <v>0.003680806404057477</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001892277261636991</v>
+        <v>0.001892277261636958</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02788108092929657</v>
+        <v>0.02788108092929654</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02974093487212993</v>
+        <v>0.02974093487212989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007614962240111043</v>
+        <v>0.007614962240110093</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01192655266552155</v>
+        <v>0.01192655266552152</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00343284316901565</v>
+        <v>0.003432843169015637</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02102573590010914</v>
+        <v>0.0210257359001087</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005666331915383871</v>
+        <v>0.005666331915383889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002005173005377087</v>
+        <v>0.002005173005377081</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05772088182153133</v>
+        <v>0.05772088182153132</v>
       </c>
       <c r="N6" t="n">
         <v>0.01455471102914444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08424536502534288</v>
+        <v>0.0842453650253429</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0454479203332398</v>
+        <v>0.04544792033323983</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02255675612915783</v>
+        <v>0.0225567561291578</v>
       </c>
       <c r="R6" t="n">
         <v>0.004549843929476795</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002756315828560565</v>
+        <v>0.002756315828560553</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02844443000755267</v>
+        <v>0.02844443000755256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03133415226565133</v>
+        <v>0.03133415226565139</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02142967072867156</v>
+        <v>0.02142967072867158</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04342096154162673</v>
+        <v>0.04342096154162677</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01572758599020942</v>
+        <v>0.01572758599020935</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03799994939759477</v>
+        <v>0.03799994939759475</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01671132664047003</v>
+        <v>0.01671132664047</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00617643679708336</v>
+        <v>0.006176436797083185</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01648799686486734</v>
+        <v>0.01648799686486735</v>
       </c>
     </row>
     <row r="7">
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001335625199176742</v>
+        <v>0.001335625199176746</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001378884239436872</v>
+        <v>0.001378884239436819</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001366044843601345</v>
+        <v>0.001366044843601331</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001457844188965286</v>
+        <v>0.001457844188965271</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001502702297467049</v>
+        <v>0.001502702297467027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001444022556666707</v>
+        <v>0.001444022556666728</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001761493726589334</v>
+        <v>0.001761493726589328</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001373319943212156</v>
+        <v>0.001373319943212133</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001373690161476443</v>
+        <v>0.001373690161476432</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00136493562147464</v>
+        <v>0.001364935621474626</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001302676800561132</v>
+        <v>0.001302676800561135</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001385937237743631</v>
+        <v>0.001385937237743624</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00133313205478333</v>
+        <v>0.001333132054783348</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001467970505489349</v>
+        <v>0.001467970505489342</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00128269838609006</v>
+        <v>0.001282698386090059</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001669689920811721</v>
+        <v>0.00166968992081172</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001332510887030166</v>
+        <v>0.001332510887030161</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001503282054606537</v>
+        <v>0.001503282054606506</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001654241058653776</v>
+        <v>0.001654241058653774</v>
       </c>
     </row>
   </sheetData>
